--- a/data/Meyer_Walaka_isotope_FFS_PH_atolls.xlsx
+++ b/data/Meyer_Walaka_isotope_FFS_PH_atolls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\popp\Documents\Manuscripts\Meyer FFS tagging and isotopes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EC0C89-9719-444F-9410-981F3BA218A3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1D322F-1E9B-4C89-AA86-49C06CFE1D85}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{6A37D781-5C4E-49C4-88ED-AB7FDA417180}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="95">
   <si>
     <t>Description</t>
   </si>
@@ -1007,6 +1007,32 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> (‰ vs VPDB)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>δ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>C (‰ vs VPDB)</t>
     </r>
   </si>
 </sst>
@@ -1151,7 +1177,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1166,15 +1191,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1221,6 +1237,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1546,7 +1574,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1567,474 +1595,474 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="17" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="21" t="s">
+      <c r="B52" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
+      <c r="A53" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="21" t="s">
+      <c r="B53" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="21" t="s">
+      <c r="A56" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="21" t="s">
+      <c r="A59" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="21" t="s">
+      <c r="A60" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="21" t="s">
+      <c r="B60" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="21" t="s">
+      <c r="A61" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B61" s="21" t="s">
+      <c r="B61" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="21" t="s">
+      <c r="A62" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="B62" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="21" t="s">
+      <c r="A63" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="17" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2053,23 +2081,27 @@
   <dimension ref="A1:BI20"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="5.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="31" width="5.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="9.140625" style="12"/>
-    <col min="34" max="46" width="9.140625" style="1"/>
-    <col min="47" max="61" width="9.140625" style="12"/>
+    <col min="1" max="1" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="5.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="31" width="5.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="9.140625" style="11"/>
+    <col min="34" max="34" width="5.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="38" max="46" width="5.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="47" max="61" width="9.140625" style="11"/>
     <col min="62" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -2079,3489 +2111,3489 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="13" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="14"/>
-      <c r="AK1" s="14"/>
-      <c r="AL1" s="14"/>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="14"/>
-      <c r="AO1" s="14"/>
-      <c r="AP1" s="14"/>
-      <c r="AQ1" s="14"/>
-      <c r="AR1" s="14"/>
-      <c r="AS1" s="14"/>
-      <c r="AT1" s="15"/>
-      <c r="AU1" s="13" t="s">
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="12"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="35"/>
+      <c r="AU1" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="AV1" s="14"/>
-      <c r="AW1" s="14"/>
-      <c r="AX1" s="14"/>
-      <c r="AY1" s="14"/>
-      <c r="AZ1" s="14"/>
-      <c r="BA1" s="14"/>
-      <c r="BB1" s="14"/>
-      <c r="BC1" s="14"/>
-      <c r="BD1" s="14"/>
-      <c r="BE1" s="14"/>
-      <c r="BF1" s="14"/>
-      <c r="BG1" s="15"/>
-    </row>
-    <row r="2" spans="1:61" s="24" customFormat="1" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
+      <c r="AY1" s="34"/>
+      <c r="AZ1" s="34"/>
+      <c r="BA1" s="34"/>
+      <c r="BB1" s="34"/>
+      <c r="BC1" s="34"/>
+      <c r="BD1" s="34"/>
+      <c r="BE1" s="34"/>
+      <c r="BF1" s="34"/>
+      <c r="BG1" s="35"/>
+    </row>
+    <row r="2" spans="1:61" s="20" customFormat="1" ht="18.75" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="18" t="s">
+      <c r="Q2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="R2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="18" t="s">
+      <c r="S2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="18" t="s">
+      <c r="T2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="U2" s="18" t="s">
+      <c r="U2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="18" t="s">
+      <c r="V2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="W2" s="18" t="s">
+      <c r="W2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="18" t="s">
+      <c r="X2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="Y2" s="18" t="s">
+      <c r="Y2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="18" t="s">
+      <c r="Z2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="AA2" s="18" t="s">
+      <c r="AA2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AB2" s="18" t="s">
+      <c r="AB2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="18" t="s">
+      <c r="AC2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="AE2" s="18" t="s">
+      <c r="AE2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="AF2" s="18" t="s">
+      <c r="AF2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="AG2" s="18" t="s">
+      <c r="AG2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="AH2" s="6" t="s">
+      <c r="AH2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="AI2" s="6" t="s">
+      <c r="AI2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="AJ2" s="6" t="s">
+      <c r="AJ2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="AK2" s="6" t="s">
+      <c r="AK2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="AL2" s="6" t="s">
+      <c r="AL2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AM2" s="6" t="s">
+      <c r="AM2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AN2" s="6" t="s">
+      <c r="AN2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="AO2" s="6" t="s">
+      <c r="AO2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="AP2" s="6" t="s">
+      <c r="AP2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AQ2" s="6" t="s">
+      <c r="AQ2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AR2" s="6" t="s">
+      <c r="AR2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AS2" s="6" t="s">
+      <c r="AS2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="AT2" s="6" t="s">
+      <c r="AT2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="AU2" s="18" t="s">
+      <c r="AU2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="AV2" s="18" t="s">
+      <c r="AV2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="AW2" s="18" t="s">
+      <c r="AW2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="AX2" s="18" t="s">
+      <c r="AX2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="AY2" s="18" t="s">
+      <c r="AY2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AZ2" s="18" t="s">
+      <c r="AZ2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="BA2" s="18" t="s">
+      <c r="BA2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="18" t="s">
+      <c r="BB2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="BC2" s="18" t="s">
+      <c r="BC2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="BD2" s="18" t="s">
+      <c r="BD2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="BE2" s="18" t="s">
+      <c r="BE2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="BF2" s="18" t="s">
+      <c r="BF2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="BG2" s="18" t="s">
+      <c r="BG2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="BH2" s="18" t="s">
+      <c r="BH2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="BI2" s="18" t="s">
+      <c r="BI2" s="14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="28">
         <v>10.4</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="31">
         <v>-13.1</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="30">
         <v>3.9903381642512072</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="15">
         <v>24</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="15">
         <v>2</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="15">
         <v>-27.2</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="15">
         <v>3.9</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="15">
         <v>23.2</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="15">
         <v>21.8</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="15">
         <v>22.9</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="15">
         <v>18.399999999999999</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="15">
         <v>19.100000000000001</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="15">
         <v>23.3</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="15">
         <v>2.2000000000000002</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="15">
         <v>9.4</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="15">
         <v>2.1</v>
       </c>
-      <c r="S3" s="19">
+      <c r="S3" s="15">
         <v>0.16</v>
       </c>
-      <c r="T3" s="19">
+      <c r="T3" s="15">
         <v>0.43</v>
       </c>
-      <c r="U3" s="19">
+      <c r="U3" s="15">
         <v>0.28000000000000003</v>
       </c>
-      <c r="V3" s="19">
+      <c r="V3" s="15">
         <v>0.23</v>
       </c>
-      <c r="W3" s="19">
+      <c r="W3" s="15">
         <v>0.38</v>
       </c>
-      <c r="X3" s="19">
+      <c r="X3" s="15">
         <v>0.21</v>
       </c>
-      <c r="Y3" s="19">
+      <c r="Y3" s="15">
         <v>0</v>
       </c>
-      <c r="Z3" s="19">
+      <c r="Z3" s="15">
         <v>0.35</v>
       </c>
-      <c r="AA3" s="19">
+      <c r="AA3" s="15">
         <v>0.34</v>
       </c>
-      <c r="AB3" s="19">
+      <c r="AB3" s="15">
         <v>0.54</v>
       </c>
-      <c r="AC3" s="19">
+      <c r="AC3" s="15">
         <v>0.06</v>
       </c>
-      <c r="AD3" s="19">
+      <c r="AD3" s="15">
         <v>0.43</v>
       </c>
-      <c r="AE3" s="19">
+      <c r="AE3" s="15">
         <v>0.19</v>
       </c>
-      <c r="AF3" s="10">
+      <c r="AF3" s="9">
         <v>0.6</v>
       </c>
-      <c r="AG3" s="10">
+      <c r="AG3" s="9">
         <v>-0.52</v>
       </c>
-      <c r="AH3" s="11">
+      <c r="AH3" s="19">
         <v>-9.8000000000000007</v>
       </c>
-      <c r="AI3" s="11">
+      <c r="AI3" s="19">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AJ3" s="11">
+      <c r="AJ3" s="19">
         <v>-8.1</v>
       </c>
-      <c r="AK3" s="11">
+      <c r="AK3" s="19">
         <v>10.5</v>
       </c>
-      <c r="AL3" s="11">
+      <c r="AL3" s="19">
         <v>-17.399999999999999</v>
       </c>
-      <c r="AM3" s="11">
+      <c r="AM3" s="19">
         <v>-19</v>
       </c>
-      <c r="AN3" s="11">
+      <c r="AN3" s="19">
         <v>-14.2</v>
       </c>
-      <c r="AO3" s="11">
+      <c r="AO3" s="19">
         <v>-10</v>
       </c>
-      <c r="AP3" s="11">
+      <c r="AP3" s="19">
         <v>-9.6999999999999993</v>
       </c>
-      <c r="AQ3" s="11">
+      <c r="AQ3" s="19">
         <v>-10.8</v>
       </c>
-      <c r="AR3" s="11">
+      <c r="AR3" s="19">
         <v>-20.3</v>
       </c>
-      <c r="AS3" s="11">
+      <c r="AS3" s="19">
         <v>-20.8</v>
       </c>
-      <c r="AT3" s="11">
+      <c r="AT3" s="19">
         <v>-12.2</v>
       </c>
-      <c r="AU3" s="23">
+      <c r="AU3" s="19">
         <v>0.76</v>
       </c>
-      <c r="AV3" s="23">
+      <c r="AV3" s="19">
         <v>0.15</v>
       </c>
-      <c r="AW3" s="23">
+      <c r="AW3" s="19">
         <v>1.17</v>
       </c>
-      <c r="AX3" s="23">
+      <c r="AX3" s="19">
         <v>0.31</v>
       </c>
-      <c r="AY3" s="23">
+      <c r="AY3" s="19">
         <v>0.22</v>
       </c>
-      <c r="AZ3" s="23">
+      <c r="AZ3" s="19">
         <v>0.03</v>
       </c>
-      <c r="BA3" s="23">
+      <c r="BA3" s="19">
         <v>0.5</v>
       </c>
-      <c r="BB3" s="23">
+      <c r="BB3" s="19">
         <v>0.23</v>
       </c>
-      <c r="BC3" s="23">
+      <c r="BC3" s="19">
         <v>0.18</v>
       </c>
-      <c r="BD3" s="23">
+      <c r="BD3" s="19">
         <v>0.28000000000000003</v>
       </c>
-      <c r="BE3" s="23">
+      <c r="BE3" s="19">
         <v>0.35</v>
       </c>
-      <c r="BF3" s="23">
+      <c r="BF3" s="19">
         <v>0.36</v>
       </c>
-      <c r="BG3" s="23">
+      <c r="BG3" s="19">
         <v>0.05</v>
       </c>
-      <c r="BH3" s="23">
+      <c r="BH3" s="19">
         <v>0.34</v>
       </c>
-      <c r="BI3" s="23">
+      <c r="BI3" s="19">
         <v>0.18</v>
       </c>
     </row>
-    <row r="4" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="28">
         <v>10.199999999999999</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="31">
         <v>-17.5</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="30">
         <v>5.2281842818428181</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="15">
         <v>25.4</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="15">
         <v>0.2</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="15">
         <v>-32.299999999999997</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="15">
         <v>3.2</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="15">
         <v>22.8</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="15">
         <v>22.4</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="15">
         <v>22.8</v>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="15">
         <v>19</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="15">
         <v>19.100000000000001</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="15">
         <v>23.2</v>
       </c>
-      <c r="P4" s="19">
+      <c r="P4" s="15">
         <v>2.9</v>
       </c>
-      <c r="Q4" s="19">
+      <c r="Q4" s="15">
         <v>10.5</v>
       </c>
-      <c r="R4" s="19">
+      <c r="R4" s="15">
         <v>2.1</v>
       </c>
-      <c r="S4" s="19">
+      <c r="S4" s="15">
         <v>0.17</v>
       </c>
-      <c r="T4" s="19">
+      <c r="T4" s="15">
         <v>0.2</v>
       </c>
-      <c r="U4" s="19">
+      <c r="U4" s="15">
         <v>0.23</v>
       </c>
-      <c r="V4" s="19">
+      <c r="V4" s="15">
         <v>0.68</v>
       </c>
-      <c r="W4" s="19">
+      <c r="W4" s="15">
         <v>0.73</v>
       </c>
-      <c r="X4" s="19">
+      <c r="X4" s="15">
         <v>0.25</v>
       </c>
-      <c r="Y4" s="19">
+      <c r="Y4" s="15">
         <v>0.61</v>
       </c>
-      <c r="Z4" s="19">
+      <c r="Z4" s="15">
         <v>0.16</v>
       </c>
-      <c r="AA4" s="19">
+      <c r="AA4" s="15">
         <v>0.09</v>
       </c>
-      <c r="AB4" s="19">
+      <c r="AB4" s="15">
         <v>0.34</v>
       </c>
-      <c r="AC4" s="19">
+      <c r="AC4" s="15">
         <v>0.51</v>
       </c>
-      <c r="AD4" s="19">
+      <c r="AD4" s="15">
         <v>0.33</v>
       </c>
-      <c r="AE4" s="19">
+      <c r="AE4" s="15">
         <v>0.27</v>
       </c>
-      <c r="AF4" s="10">
+      <c r="AF4" s="9">
         <v>0.31</v>
       </c>
-      <c r="AG4" s="10">
+      <c r="AG4" s="9">
         <v>-0.32</v>
       </c>
-      <c r="AH4" s="11">
+      <c r="AH4" s="19">
         <v>-12.7</v>
       </c>
-      <c r="AI4" s="11">
+      <c r="AI4" s="19">
         <v>-1.6</v>
       </c>
-      <c r="AJ4" s="11">
+      <c r="AJ4" s="19">
         <v>-10</v>
       </c>
-      <c r="AK4" s="11">
+      <c r="AK4" s="19">
         <v>9.6999999999999993</v>
       </c>
-      <c r="AL4" s="11">
+      <c r="AL4" s="19">
         <v>-17.100000000000001</v>
       </c>
-      <c r="AM4" s="11">
+      <c r="AM4" s="19">
         <v>-21.5</v>
       </c>
-      <c r="AN4" s="11">
+      <c r="AN4" s="19">
         <v>-16.3</v>
       </c>
-      <c r="AO4" s="11">
+      <c r="AO4" s="19">
         <v>-12.4</v>
       </c>
-      <c r="AP4" s="11">
+      <c r="AP4" s="19">
         <v>-13.2</v>
       </c>
-      <c r="AQ4" s="11">
+      <c r="AQ4" s="19">
         <v>-13.4</v>
       </c>
-      <c r="AR4" s="11">
+      <c r="AR4" s="19">
         <v>-22.1</v>
       </c>
-      <c r="AS4" s="11">
+      <c r="AS4" s="19">
         <v>-23.3</v>
       </c>
-      <c r="AT4" s="11">
+      <c r="AT4" s="19">
         <v>-15.1</v>
       </c>
-      <c r="AU4" s="23">
+      <c r="AU4" s="19">
         <v>0.81</v>
       </c>
-      <c r="AV4" s="23">
+      <c r="AV4" s="19">
         <v>0.15</v>
       </c>
-      <c r="AW4" s="23">
+      <c r="AW4" s="19">
         <v>0.15</v>
       </c>
-      <c r="AX4" s="23">
+      <c r="AX4" s="19">
         <v>0.98</v>
       </c>
-      <c r="AY4" s="23">
+      <c r="AY4" s="19">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AZ4" s="23">
+      <c r="AZ4" s="19">
         <v>0.3</v>
       </c>
-      <c r="BA4" s="23">
+      <c r="BA4" s="19">
         <v>0.3</v>
       </c>
-      <c r="BB4" s="23">
+      <c r="BB4" s="19">
         <v>0.1</v>
       </c>
-      <c r="BC4" s="23">
+      <c r="BC4" s="19">
         <v>0.2</v>
       </c>
-      <c r="BD4" s="23">
+      <c r="BD4" s="19">
         <v>0.05</v>
       </c>
-      <c r="BE4" s="23">
+      <c r="BE4" s="19">
         <v>0.86</v>
       </c>
-      <c r="BF4" s="23">
+      <c r="BF4" s="19">
         <v>0.71</v>
       </c>
-      <c r="BG4" s="23">
+      <c r="BG4" s="19">
         <v>0.21</v>
       </c>
-      <c r="BH4" s="23">
+      <c r="BH4" s="19">
         <v>0.35</v>
       </c>
-      <c r="BI4" s="23">
+      <c r="BI4" s="19">
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="28">
         <v>10.6</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="31">
         <v>-14</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="30">
         <v>3.9073556797020488</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="15">
         <v>25.5</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="15">
         <v>2.1</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="15">
         <v>-24.6</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="15">
         <v>3.4</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="15">
         <v>21.2</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="15">
         <v>21.9</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="15">
         <v>22.1</v>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="15">
         <v>18.7</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="15">
         <v>19</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="15">
         <v>23</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="15">
         <v>2.1</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="15">
         <v>10.6</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="15">
         <v>3.9</v>
       </c>
-      <c r="S5" s="19">
+      <c r="S5" s="15">
         <v>0.21</v>
       </c>
-      <c r="T5" s="19">
+      <c r="T5" s="15">
         <v>0.75</v>
       </c>
-      <c r="U5" s="19">
+      <c r="U5" s="15">
         <v>0.42</v>
       </c>
-      <c r="V5" s="19">
+      <c r="V5" s="15">
         <v>0.69</v>
       </c>
-      <c r="W5" s="19">
+      <c r="W5" s="15">
         <v>1.1399999999999999</v>
       </c>
-      <c r="X5" s="19">
+      <c r="X5" s="15">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Y5" s="19">
+      <c r="Y5" s="15">
         <v>0.86</v>
       </c>
-      <c r="Z5" s="19">
+      <c r="Z5" s="15">
         <v>0.35</v>
       </c>
-      <c r="AA5" s="19">
+      <c r="AA5" s="15">
         <v>0.37</v>
       </c>
-      <c r="AB5" s="19">
+      <c r="AB5" s="15">
         <v>0.12</v>
       </c>
-      <c r="AC5" s="19">
+      <c r="AC5" s="15">
         <v>0.36</v>
       </c>
-      <c r="AD5" s="19">
+      <c r="AD5" s="15">
         <v>0.83</v>
       </c>
-      <c r="AE5" s="19">
+      <c r="AE5" s="15">
         <v>0.54</v>
       </c>
-      <c r="AF5" s="10">
+      <c r="AF5" s="9">
         <v>0.22</v>
       </c>
-      <c r="AG5" s="10">
+      <c r="AG5" s="9">
         <v>-0.53</v>
       </c>
-      <c r="AH5" s="11">
+      <c r="AH5" s="19">
         <v>-11.6</v>
       </c>
-      <c r="AI5" s="11">
+      <c r="AI5" s="19">
         <v>-2.1</v>
       </c>
-      <c r="AJ5" s="11">
+      <c r="AJ5" s="19">
         <v>-8.3000000000000007</v>
       </c>
-      <c r="AK5" s="11">
+      <c r="AK5" s="19">
         <v>9</v>
       </c>
-      <c r="AL5" s="11">
+      <c r="AL5" s="19">
         <v>-18.2</v>
       </c>
-      <c r="AM5" s="11">
+      <c r="AM5" s="19">
         <v>-20</v>
       </c>
-      <c r="AN5" s="11">
+      <c r="AN5" s="19">
         <v>-13.9</v>
       </c>
-      <c r="AO5" s="11">
+      <c r="AO5" s="19">
         <v>-10.5</v>
       </c>
-      <c r="AP5" s="11">
+      <c r="AP5" s="19">
         <v>-11</v>
       </c>
-      <c r="AQ5" s="11">
+      <c r="AQ5" s="19">
         <v>-9.6</v>
       </c>
-      <c r="AR5" s="11">
+      <c r="AR5" s="19">
         <v>-20.2</v>
       </c>
-      <c r="AS5" s="11">
+      <c r="AS5" s="19">
         <v>-22.1</v>
       </c>
-      <c r="AT5" s="11">
+      <c r="AT5" s="19">
         <v>-12.3</v>
       </c>
-      <c r="AU5" s="23">
+      <c r="AU5" s="19">
         <v>0.21</v>
       </c>
-      <c r="AV5" s="23">
+      <c r="AV5" s="19">
         <v>0.87</v>
       </c>
-      <c r="AW5" s="23">
+      <c r="AW5" s="19">
         <v>0.56999999999999995</v>
       </c>
-      <c r="AX5" s="23">
+      <c r="AX5" s="19">
         <v>0.52</v>
       </c>
-      <c r="AY5" s="23">
+      <c r="AY5" s="19">
         <v>1</v>
       </c>
-      <c r="AZ5" s="23">
+      <c r="AZ5" s="19">
         <v>0.09</v>
       </c>
-      <c r="BA5" s="23">
+      <c r="BA5" s="19">
         <v>0.44</v>
       </c>
-      <c r="BB5" s="23">
+      <c r="BB5" s="19">
         <v>0.09</v>
       </c>
-      <c r="BC5" s="23">
+      <c r="BC5" s="19">
         <v>0.15</v>
       </c>
-      <c r="BD5" s="23">
+      <c r="BD5" s="19">
         <v>0.28000000000000003</v>
       </c>
-      <c r="BE5" s="23">
+      <c r="BE5" s="19">
         <v>0.44</v>
       </c>
-      <c r="BF5" s="23">
+      <c r="BF5" s="19">
         <v>0.59</v>
       </c>
-      <c r="BG5" s="23">
+      <c r="BG5" s="19">
         <v>0.35</v>
       </c>
-      <c r="BH5" s="23">
+      <c r="BH5" s="19">
         <v>0.41</v>
       </c>
-      <c r="BI5" s="23">
+      <c r="BI5" s="19">
         <v>0.66</v>
       </c>
     </row>
-    <row r="6" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="28">
         <v>9.6999999999999993</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="31">
         <v>-16.7</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="30">
         <v>4.1975088967971521</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="15">
         <v>23.8</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="15">
         <v>1.4</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="15">
         <v>-27.1</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="15">
         <v>3</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="15">
         <v>19.2</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="15">
         <v>20.6</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="15">
         <v>20.6</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="15">
         <v>17.7</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="15">
         <v>17</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="15">
         <v>22.3</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="15">
         <v>1.7</v>
       </c>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19">
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15">
         <v>2.4</v>
       </c>
-      <c r="S6" s="19">
+      <c r="S6" s="15">
         <v>0.2</v>
       </c>
-      <c r="T6" s="19">
+      <c r="T6" s="15">
         <v>0.26</v>
       </c>
-      <c r="U6" s="19">
+      <c r="U6" s="15">
         <v>0.53</v>
       </c>
-      <c r="V6" s="19">
+      <c r="V6" s="15">
         <v>0.3</v>
       </c>
-      <c r="W6" s="19">
+      <c r="W6" s="15">
         <v>0.79</v>
       </c>
-      <c r="X6" s="19">
+      <c r="X6" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Y6" s="19">
+      <c r="Y6" s="15">
         <v>0.2</v>
       </c>
-      <c r="Z6" s="19">
+      <c r="Z6" s="15">
         <v>0.08</v>
       </c>
-      <c r="AA6" s="19">
+      <c r="AA6" s="15">
         <v>0.22</v>
       </c>
-      <c r="AB6" s="19">
+      <c r="AB6" s="15">
         <v>0.25</v>
       </c>
-      <c r="AC6" s="19">
+      <c r="AC6" s="15">
         <v>0.71</v>
       </c>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="19">
+      <c r="AD6" s="15"/>
+      <c r="AE6" s="15">
         <v>0.1</v>
       </c>
-      <c r="AF6" s="10">
+      <c r="AF6" s="9">
         <v>0.4</v>
       </c>
-      <c r="AG6" s="10">
+      <c r="AG6" s="9">
         <v>-0.83</v>
       </c>
-      <c r="AH6" s="11">
+      <c r="AH6" s="19">
         <v>-13.2</v>
       </c>
-      <c r="AI6" s="11">
+      <c r="AI6" s="19">
         <v>-6.7</v>
       </c>
-      <c r="AJ6" s="11">
+      <c r="AJ6" s="19">
         <v>-8.6</v>
       </c>
-      <c r="AK6" s="11">
+      <c r="AK6" s="19">
         <v>3.5</v>
       </c>
-      <c r="AL6" s="11">
+      <c r="AL6" s="19">
         <v>-18.899999999999999</v>
       </c>
-      <c r="AM6" s="11">
+      <c r="AM6" s="19">
         <v>-20.9</v>
       </c>
-      <c r="AN6" s="11">
+      <c r="AN6" s="19">
         <v>-15.9</v>
       </c>
-      <c r="AO6" s="11">
+      <c r="AO6" s="19">
         <v>-11.9</v>
       </c>
-      <c r="AP6" s="11">
+      <c r="AP6" s="19">
         <v>-12.3</v>
       </c>
-      <c r="AQ6" s="11">
+      <c r="AQ6" s="19">
         <v>-12.2</v>
       </c>
-      <c r="AR6" s="11">
+      <c r="AR6" s="19">
         <v>-23.3</v>
       </c>
-      <c r="AS6" s="11">
+      <c r="AS6" s="19">
         <v>-22</v>
       </c>
-      <c r="AT6" s="11">
+      <c r="AT6" s="19">
         <v>-12.4</v>
       </c>
-      <c r="AU6" s="23">
+      <c r="AU6" s="19">
         <v>0.19</v>
       </c>
-      <c r="AV6" s="23">
+      <c r="AV6" s="19">
         <v>0.56999999999999995</v>
       </c>
-      <c r="AW6" s="23">
+      <c r="AW6" s="19">
         <v>0.62</v>
       </c>
-      <c r="AX6" s="23">
+      <c r="AX6" s="19">
         <v>0.41</v>
       </c>
-      <c r="AY6" s="23">
+      <c r="AY6" s="19">
         <v>0.26</v>
       </c>
-      <c r="AZ6" s="23">
+      <c r="AZ6" s="19">
         <v>0.25</v>
       </c>
-      <c r="BA6" s="23">
+      <c r="BA6" s="19">
         <v>0.49</v>
       </c>
-      <c r="BB6" s="23">
+      <c r="BB6" s="19">
         <v>0.3</v>
       </c>
-      <c r="BC6" s="23">
+      <c r="BC6" s="19">
         <v>0.28999999999999998</v>
       </c>
-      <c r="BD6" s="23">
+      <c r="BD6" s="19">
         <v>0.19</v>
       </c>
-      <c r="BE6" s="23">
+      <c r="BE6" s="19">
         <v>0.73</v>
       </c>
-      <c r="BF6" s="23">
+      <c r="BF6" s="19">
         <v>0.57999999999999996</v>
       </c>
-      <c r="BG6" s="23">
+      <c r="BG6" s="19">
         <v>0.18</v>
       </c>
-      <c r="BH6" s="23">
+      <c r="BH6" s="19">
         <v>0.37</v>
       </c>
-      <c r="BI6" s="23">
+      <c r="BI6" s="19">
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="28">
         <v>10.5</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="31">
         <v>-14.6</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="30">
         <v>3.8440366972477062</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="15">
         <v>25.5</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="15">
         <v>1.2</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="15">
         <v>-26.5</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="15">
         <v>3.4</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="15">
         <v>21.7</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="15">
         <v>22.7</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="15">
         <v>22.7</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="15">
         <v>19.2</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="15">
         <v>19.8</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="15">
         <v>24.7</v>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="15">
         <v>2.4</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="15">
         <v>9.8000000000000007</v>
       </c>
-      <c r="R7" s="19">
+      <c r="R7" s="15">
         <v>3.8</v>
       </c>
-      <c r="S7" s="19">
+      <c r="S7" s="15">
         <v>0.11</v>
       </c>
-      <c r="T7" s="19">
+      <c r="T7" s="15">
         <v>0.17</v>
       </c>
-      <c r="U7" s="19">
+      <c r="U7" s="15">
         <v>0.92</v>
       </c>
-      <c r="V7" s="19">
+      <c r="V7" s="15">
         <v>0.11</v>
       </c>
-      <c r="W7" s="19">
+      <c r="W7" s="15">
         <v>0.56999999999999995</v>
       </c>
-      <c r="X7" s="19">
+      <c r="X7" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Y7" s="19">
+      <c r="Y7" s="15">
         <v>0.18</v>
       </c>
-      <c r="Z7" s="19">
+      <c r="Z7" s="15">
         <v>0.17</v>
       </c>
-      <c r="AA7" s="19">
+      <c r="AA7" s="15">
         <v>0.11</v>
       </c>
-      <c r="AB7" s="19">
+      <c r="AB7" s="15">
         <v>0.05</v>
       </c>
-      <c r="AC7" s="19">
+      <c r="AC7" s="15">
         <v>0.52</v>
       </c>
-      <c r="AD7" s="19">
+      <c r="AD7" s="15">
         <v>0.75</v>
       </c>
-      <c r="AE7" s="19">
+      <c r="AE7" s="15">
         <v>0.08</v>
       </c>
-      <c r="AF7" s="10">
+      <c r="AF7" s="9">
         <v>0.35</v>
       </c>
-      <c r="AG7" s="10">
+      <c r="AG7" s="9">
         <v>-0.38</v>
       </c>
-      <c r="AH7" s="11">
+      <c r="AH7" s="19">
         <v>-11.7</v>
       </c>
-      <c r="AI7" s="11">
+      <c r="AI7" s="19">
         <v>-2.9</v>
       </c>
-      <c r="AJ7" s="11">
+      <c r="AJ7" s="19">
         <v>-7.5</v>
       </c>
-      <c r="AK7" s="11">
+      <c r="AK7" s="19">
         <v>10.3</v>
       </c>
-      <c r="AL7" s="11">
+      <c r="AL7" s="19">
         <v>-18.7</v>
       </c>
-      <c r="AM7" s="11">
+      <c r="AM7" s="19">
         <v>-20.2</v>
       </c>
-      <c r="AN7" s="11">
+      <c r="AN7" s="19">
         <v>-15.2</v>
       </c>
-      <c r="AO7" s="11">
+      <c r="AO7" s="19">
         <v>-11.3</v>
       </c>
-      <c r="AP7" s="11">
+      <c r="AP7" s="19">
         <v>-11.6</v>
       </c>
-      <c r="AQ7" s="11">
+      <c r="AQ7" s="19">
         <v>-10.9</v>
       </c>
-      <c r="AR7" s="11">
+      <c r="AR7" s="19">
         <v>-21.3</v>
       </c>
-      <c r="AS7" s="11">
+      <c r="AS7" s="19">
         <v>-21.6</v>
       </c>
-      <c r="AT7" s="11">
+      <c r="AT7" s="19">
         <v>-10.9</v>
       </c>
-      <c r="AU7" s="23">
+      <c r="AU7" s="19">
         <v>0.34</v>
       </c>
-      <c r="AV7" s="23">
+      <c r="AV7" s="19">
         <v>0.35</v>
       </c>
-      <c r="AW7" s="23">
+      <c r="AW7" s="19">
         <v>0.13</v>
       </c>
-      <c r="AX7" s="23">
+      <c r="AX7" s="19">
         <v>0.05</v>
       </c>
-      <c r="AY7" s="23">
+      <c r="AY7" s="19">
         <v>0.39</v>
       </c>
-      <c r="AZ7" s="23">
+      <c r="AZ7" s="19">
         <v>0.13</v>
       </c>
-      <c r="BA7" s="23">
+      <c r="BA7" s="19">
         <v>0.59</v>
       </c>
-      <c r="BB7" s="23">
+      <c r="BB7" s="19">
         <v>0.23</v>
       </c>
-      <c r="BC7" s="23">
+      <c r="BC7" s="19">
         <v>0.15</v>
       </c>
-      <c r="BD7" s="23">
+      <c r="BD7" s="19">
         <v>0.28999999999999998</v>
       </c>
-      <c r="BE7" s="23">
+      <c r="BE7" s="19">
         <v>0.88</v>
       </c>
-      <c r="BF7" s="23">
+      <c r="BF7" s="19">
         <v>0.47</v>
       </c>
-      <c r="BG7" s="23">
+      <c r="BG7" s="19">
         <v>0.06</v>
       </c>
-      <c r="BH7" s="23">
+      <c r="BH7" s="19">
         <v>0.28999999999999998</v>
       </c>
-      <c r="BI7" s="23">
+      <c r="BI7" s="19">
         <v>0.41</v>
       </c>
     </row>
-    <row r="8" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="28">
         <v>10.1</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="31">
         <v>-16.100000000000001</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="30">
         <v>4.0273224043715841</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="15">
         <v>24.1</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="15">
         <v>-0.1</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="15">
         <v>-28.5</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="15">
         <v>1.4</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="15">
         <v>19.100000000000001</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="15">
         <v>21.4</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="15">
         <v>22.5</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="15">
         <v>19.399999999999999</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="15">
         <v>18.399999999999999</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="15">
         <v>23</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="15">
         <v>2.2999999999999998</v>
       </c>
-      <c r="Q8" s="19">
+      <c r="Q8" s="15">
         <v>10</v>
       </c>
-      <c r="R8" s="19">
+      <c r="R8" s="15">
         <v>3.3</v>
       </c>
-      <c r="S8" s="19">
+      <c r="S8" s="15">
         <v>0.36</v>
       </c>
-      <c r="T8" s="19">
+      <c r="T8" s="15">
         <v>0.31</v>
       </c>
-      <c r="U8" s="19">
+      <c r="U8" s="15">
         <v>0.36</v>
       </c>
-      <c r="V8" s="19">
+      <c r="V8" s="15">
         <v>0.12</v>
       </c>
-      <c r="W8" s="19">
+      <c r="W8" s="15">
         <v>0.52</v>
       </c>
-      <c r="X8" s="19">
+      <c r="X8" s="15">
         <v>0.52</v>
       </c>
-      <c r="Y8" s="19">
+      <c r="Y8" s="15">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Z8" s="19">
+      <c r="Z8" s="15">
         <v>0.18</v>
       </c>
-      <c r="AA8" s="19">
+      <c r="AA8" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AB8" s="19">
+      <c r="AB8" s="15">
         <v>0.04</v>
       </c>
-      <c r="AC8" s="19">
+      <c r="AC8" s="15">
         <v>0.1</v>
       </c>
-      <c r="AD8" s="19">
+      <c r="AD8" s="15">
         <v>0.66</v>
       </c>
-      <c r="AE8" s="19">
+      <c r="AE8" s="15">
         <v>0.1</v>
       </c>
-      <c r="AF8" s="10">
+      <c r="AF8" s="9">
         <v>0.53</v>
       </c>
-      <c r="AG8" s="10">
+      <c r="AG8" s="9">
         <v>0.83</v>
       </c>
-      <c r="AH8" s="11">
+      <c r="AH8" s="19">
         <v>-14.1</v>
       </c>
-      <c r="AI8" s="11">
+      <c r="AI8" s="19">
         <v>-5.9</v>
       </c>
-      <c r="AJ8" s="11">
+      <c r="AJ8" s="19">
         <v>-9.6999999999999993</v>
       </c>
-      <c r="AK8" s="11">
+      <c r="AK8" s="19">
         <v>5.6</v>
       </c>
-      <c r="AL8" s="11">
+      <c r="AL8" s="19">
         <v>-19</v>
       </c>
-      <c r="AM8" s="11">
+      <c r="AM8" s="19">
         <v>-21.1</v>
       </c>
-      <c r="AN8" s="11">
+      <c r="AN8" s="19">
         <v>-15.6</v>
       </c>
-      <c r="AO8" s="11">
+      <c r="AO8" s="19">
         <v>-11.7</v>
       </c>
-      <c r="AP8" s="11">
+      <c r="AP8" s="19">
         <v>-13</v>
       </c>
-      <c r="AQ8" s="11">
+      <c r="AQ8" s="19">
         <v>-12.6</v>
       </c>
-      <c r="AR8" s="11">
+      <c r="AR8" s="19">
         <v>-22.9</v>
       </c>
-      <c r="AS8" s="11">
+      <c r="AS8" s="19">
         <v>-22.4</v>
       </c>
-      <c r="AT8" s="11">
+      <c r="AT8" s="19">
         <v>-12.7</v>
       </c>
-      <c r="AU8" s="23">
+      <c r="AU8" s="19">
         <v>0.59</v>
       </c>
-      <c r="AV8" s="23">
+      <c r="AV8" s="19">
         <v>0.32</v>
       </c>
-      <c r="AW8" s="23">
+      <c r="AW8" s="19">
         <v>0.71</v>
       </c>
-      <c r="AX8" s="23">
+      <c r="AX8" s="19">
         <v>0.81</v>
       </c>
-      <c r="AY8" s="23">
+      <c r="AY8" s="19">
         <v>0.2</v>
       </c>
-      <c r="AZ8" s="23">
+      <c r="AZ8" s="19">
         <v>0.12</v>
       </c>
-      <c r="BA8" s="23">
+      <c r="BA8" s="19">
         <v>0.77</v>
       </c>
-      <c r="BB8" s="23">
+      <c r="BB8" s="19">
         <v>0.08</v>
       </c>
-      <c r="BC8" s="23">
+      <c r="BC8" s="19">
         <v>0.37</v>
       </c>
-      <c r="BD8" s="23">
+      <c r="BD8" s="19">
         <v>0.47</v>
       </c>
-      <c r="BE8" s="23">
+      <c r="BE8" s="19">
         <v>0.18</v>
       </c>
-      <c r="BF8" s="23">
+      <c r="BF8" s="19">
         <v>0.2</v>
       </c>
-      <c r="BG8" s="23">
+      <c r="BG8" s="19">
         <v>0.12</v>
       </c>
-      <c r="BH8" s="23">
+      <c r="BH8" s="19">
         <v>0.36</v>
       </c>
-      <c r="BI8" s="23">
+      <c r="BI8" s="19">
         <v>0.26</v>
       </c>
     </row>
-    <row r="9" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="28">
         <v>10.9</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="31">
         <v>-13.4</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="30">
         <v>3.7524242424242429</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="15">
         <v>24.7</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="15">
         <v>0.7</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="15">
         <v>-28.8</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="15">
         <v>2</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="15">
         <v>23</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="15">
         <v>22.9</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="15">
         <v>23.7</v>
       </c>
-      <c r="M9" s="19">
+      <c r="M9" s="15">
         <v>17.8</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="15">
         <v>18.600000000000001</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="15">
         <v>24.1</v>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="15">
         <v>3.9</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="Q9" s="15">
         <v>8.4</v>
       </c>
-      <c r="R9" s="19">
+      <c r="R9" s="15">
         <v>2.5</v>
       </c>
-      <c r="S9" s="19">
+      <c r="S9" s="15">
         <v>0.54</v>
       </c>
-      <c r="T9" s="19">
+      <c r="T9" s="15">
         <v>0.37</v>
       </c>
-      <c r="U9" s="19">
+      <c r="U9" s="15">
         <v>0.77</v>
       </c>
-      <c r="V9" s="19">
+      <c r="V9" s="15">
         <v>0.09</v>
       </c>
-      <c r="W9" s="19">
+      <c r="W9" s="15">
         <v>0.7</v>
       </c>
-      <c r="X9" s="19">
+      <c r="X9" s="15">
         <v>0.21</v>
       </c>
-      <c r="Y9" s="19">
+      <c r="Y9" s="15">
         <v>0.63</v>
       </c>
-      <c r="Z9" s="19">
+      <c r="Z9" s="15">
         <v>0.15</v>
       </c>
-      <c r="AA9" s="19">
+      <c r="AA9" s="15">
         <v>0.32</v>
       </c>
-      <c r="AB9" s="19">
+      <c r="AB9" s="15">
         <v>0.23</v>
       </c>
-      <c r="AC9" s="19">
+      <c r="AC9" s="15">
         <v>0.39</v>
       </c>
-      <c r="AD9" s="19">
+      <c r="AD9" s="15">
         <v>0.25</v>
       </c>
-      <c r="AE9" s="19">
+      <c r="AE9" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AF9" s="10">
+      <c r="AF9" s="9">
         <v>0.4</v>
       </c>
-      <c r="AG9" s="10">
+      <c r="AG9" s="9">
         <v>-0.54</v>
       </c>
-      <c r="AH9" s="11">
+      <c r="AH9" s="19">
         <v>-10.3</v>
       </c>
-      <c r="AI9" s="11">
+      <c r="AI9" s="19">
         <v>0.6</v>
       </c>
-      <c r="AJ9" s="11">
+      <c r="AJ9" s="19">
         <v>-7.8</v>
       </c>
-      <c r="AK9" s="11">
+      <c r="AK9" s="19">
         <v>9.8000000000000007</v>
       </c>
-      <c r="AL9" s="11">
+      <c r="AL9" s="19">
         <v>-17.8</v>
       </c>
-      <c r="AM9" s="11">
+      <c r="AM9" s="19">
         <v>-19.2</v>
       </c>
-      <c r="AN9" s="11">
+      <c r="AN9" s="19">
         <v>-14.5</v>
       </c>
-      <c r="AO9" s="11">
+      <c r="AO9" s="19">
         <v>-10.7</v>
       </c>
-      <c r="AP9" s="11">
+      <c r="AP9" s="19">
         <v>-9.3000000000000007</v>
       </c>
-      <c r="AQ9" s="11">
+      <c r="AQ9" s="19">
         <v>-9.5</v>
       </c>
-      <c r="AR9" s="11">
+      <c r="AR9" s="19">
         <v>-21.1</v>
       </c>
-      <c r="AS9" s="11">
+      <c r="AS9" s="19">
         <v>-22.5</v>
       </c>
-      <c r="AT9" s="11">
+      <c r="AT9" s="19">
         <v>-12.6</v>
       </c>
-      <c r="AU9" s="23">
+      <c r="AU9" s="19">
         <v>0.74</v>
       </c>
-      <c r="AV9" s="23">
+      <c r="AV9" s="19">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AW9" s="23">
+      <c r="AW9" s="19">
         <v>0.68</v>
       </c>
-      <c r="AX9" s="23">
+      <c r="AX9" s="19">
         <v>0.79</v>
       </c>
-      <c r="AY9" s="23">
+      <c r="AY9" s="19">
         <v>0.57999999999999996</v>
       </c>
-      <c r="AZ9" s="23">
+      <c r="AZ9" s="19">
         <v>0.56000000000000005</v>
       </c>
-      <c r="BA9" s="23">
+      <c r="BA9" s="19">
         <v>0.41</v>
       </c>
-      <c r="BB9" s="23">
+      <c r="BB9" s="19">
         <v>0.5</v>
       </c>
-      <c r="BC9" s="23">
+      <c r="BC9" s="19">
         <v>0.27</v>
       </c>
-      <c r="BD9" s="23">
+      <c r="BD9" s="19">
         <v>0.16</v>
       </c>
-      <c r="BE9" s="23">
+      <c r="BE9" s="19">
         <v>0.31</v>
       </c>
-      <c r="BF9" s="23">
+      <c r="BF9" s="19">
         <v>0.45</v>
       </c>
-      <c r="BG9" s="23">
+      <c r="BG9" s="19">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BH9" s="23">
+      <c r="BH9" s="19">
         <v>0.41</v>
       </c>
-      <c r="BI9" s="23">
+      <c r="BI9" s="19">
         <v>0.59</v>
       </c>
     </row>
-    <row r="10" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="28">
         <v>10</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="31">
         <v>-16.100000000000001</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="30">
         <v>4.036306460834763</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="15">
         <v>24.7</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="15">
         <v>-1.7</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="15">
         <v>-31.4</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="15">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="15">
         <v>22.3</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="15">
         <v>22.7</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="15">
         <v>22.6</v>
       </c>
-      <c r="M10" s="19">
+      <c r="M10" s="15">
         <v>18.5</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="15">
         <v>19.2</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="15">
         <v>23.9</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="15">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="15">
         <v>10.7</v>
       </c>
-      <c r="R10" s="19">
+      <c r="R10" s="15">
         <v>2.4</v>
       </c>
-      <c r="S10" s="19">
+      <c r="S10" s="15">
         <v>0.23</v>
       </c>
-      <c r="T10" s="19">
+      <c r="T10" s="15">
         <v>0.36</v>
       </c>
-      <c r="U10" s="19">
+      <c r="U10" s="15">
         <v>0.45</v>
       </c>
-      <c r="V10" s="19">
+      <c r="V10" s="15">
         <v>0.5</v>
       </c>
-      <c r="W10" s="19">
+      <c r="W10" s="15">
         <v>0.3</v>
       </c>
-      <c r="X10" s="19">
+      <c r="X10" s="15">
         <v>0.22</v>
       </c>
-      <c r="Y10" s="19">
+      <c r="Y10" s="15">
         <v>0.79</v>
       </c>
-      <c r="Z10" s="19">
+      <c r="Z10" s="15">
         <v>0.12</v>
       </c>
-      <c r="AA10" s="19">
+      <c r="AA10" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AB10" s="19">
+      <c r="AB10" s="15">
         <v>0.02</v>
       </c>
-      <c r="AC10" s="19">
+      <c r="AC10" s="15">
         <v>0.92</v>
       </c>
-      <c r="AD10" s="19">
+      <c r="AD10" s="15">
         <v>0.47</v>
       </c>
-      <c r="AE10" s="19">
+      <c r="AE10" s="15">
         <v>0.39</v>
       </c>
-      <c r="AF10" s="10">
+      <c r="AF10" s="9">
         <v>0.3</v>
       </c>
-      <c r="AG10" s="10">
+      <c r="AG10" s="9">
         <v>-0.67</v>
       </c>
-      <c r="AH10" s="11">
+      <c r="AH10" s="19">
         <v>-13.1</v>
       </c>
-      <c r="AI10" s="11">
+      <c r="AI10" s="19">
         <v>-3.6</v>
       </c>
-      <c r="AJ10" s="11">
+      <c r="AJ10" s="19">
         <v>-9.6999999999999993</v>
       </c>
-      <c r="AK10" s="11">
+      <c r="AK10" s="19">
         <v>5.6</v>
       </c>
-      <c r="AL10" s="11">
+      <c r="AL10" s="19">
         <v>-19.8</v>
       </c>
-      <c r="AM10" s="11">
+      <c r="AM10" s="19">
         <v>-21.5</v>
       </c>
-      <c r="AN10" s="11">
+      <c r="AN10" s="19">
         <v>-15.9</v>
       </c>
-      <c r="AO10" s="11">
+      <c r="AO10" s="19">
         <v>-12.1</v>
       </c>
-      <c r="AP10" s="11">
+      <c r="AP10" s="19">
         <v>-13</v>
       </c>
-      <c r="AQ10" s="11">
+      <c r="AQ10" s="19">
         <v>-12.9</v>
       </c>
-      <c r="AR10" s="11">
+      <c r="AR10" s="19">
         <v>-22.8</v>
       </c>
-      <c r="AS10" s="11">
+      <c r="AS10" s="19">
         <v>-22.2</v>
       </c>
-      <c r="AT10" s="11">
+      <c r="AT10" s="19">
         <v>-12.9</v>
       </c>
-      <c r="AU10" s="23">
+      <c r="AU10" s="19">
         <v>0.3</v>
       </c>
-      <c r="AV10" s="23">
+      <c r="AV10" s="19">
         <v>0.22</v>
       </c>
-      <c r="AW10" s="23">
+      <c r="AW10" s="19">
         <v>0.38</v>
       </c>
-      <c r="AX10" s="23">
+      <c r="AX10" s="19">
         <v>0.51</v>
       </c>
-      <c r="AY10" s="23">
+      <c r="AY10" s="19">
         <v>0.22</v>
       </c>
-      <c r="AZ10" s="23">
+      <c r="AZ10" s="19">
         <v>0.19</v>
       </c>
-      <c r="BA10" s="23">
+      <c r="BA10" s="19">
         <v>0.1</v>
       </c>
-      <c r="BB10" s="23">
+      <c r="BB10" s="19">
         <v>0.37</v>
       </c>
-      <c r="BC10" s="23">
+      <c r="BC10" s="19">
         <v>0.26</v>
       </c>
-      <c r="BD10" s="23">
+      <c r="BD10" s="19">
         <v>0.13</v>
       </c>
-      <c r="BE10" s="23">
+      <c r="BE10" s="19">
         <v>0.67</v>
       </c>
-      <c r="BF10" s="23">
+      <c r="BF10" s="19">
         <v>0.46</v>
       </c>
-      <c r="BG10" s="23">
+      <c r="BG10" s="19">
         <v>0.08</v>
       </c>
-      <c r="BH10" s="23">
+      <c r="BH10" s="19">
         <v>0.28000000000000003</v>
       </c>
-      <c r="BI10" s="23">
+      <c r="BI10" s="19">
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="28">
         <v>11.2</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="31">
         <v>-13.8</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="30">
         <v>4.6393617021276601</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="15">
         <v>23.3</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="15">
         <v>3.2</v>
       </c>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19">
+      <c r="H11" s="15"/>
+      <c r="I11" s="15">
         <v>2.9</v>
       </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19">
+      <c r="J11" s="15"/>
+      <c r="K11" s="15">
         <v>20.8</v>
       </c>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19">
+      <c r="L11" s="15"/>
+      <c r="M11" s="15">
         <v>15.9</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="15">
         <v>16.100000000000001</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="15">
         <v>20</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="15">
         <v>1.6</v>
       </c>
-      <c r="Q11" s="19">
+      <c r="Q11" s="15">
         <v>12.3</v>
       </c>
-      <c r="R11" s="19">
+      <c r="R11" s="15">
         <v>2.9</v>
       </c>
-      <c r="S11" s="19">
+      <c r="S11" s="15">
         <v>0.27</v>
       </c>
-      <c r="T11" s="19">
+      <c r="T11" s="15">
         <v>0.27</v>
       </c>
-      <c r="U11" s="19"/>
-      <c r="V11" s="19">
+      <c r="U11" s="15"/>
+      <c r="V11" s="15">
         <v>0.73</v>
       </c>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19">
+      <c r="W11" s="15"/>
+      <c r="X11" s="15">
         <v>0.15</v>
       </c>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19">
+      <c r="Y11" s="15"/>
+      <c r="Z11" s="15">
         <v>0.19</v>
       </c>
-      <c r="AA11" s="19">
+      <c r="AA11" s="15">
         <v>0.3</v>
       </c>
-      <c r="AB11" s="19">
+      <c r="AB11" s="15">
         <v>0.08</v>
       </c>
-      <c r="AC11" s="19">
+      <c r="AC11" s="15">
         <v>0.22</v>
       </c>
-      <c r="AD11" s="19">
+      <c r="AD11" s="15">
         <v>0.77</v>
       </c>
-      <c r="AE11" s="19">
+      <c r="AE11" s="15">
         <v>0.37</v>
       </c>
-      <c r="AF11" s="10">
+      <c r="AF11" s="9">
         <v>0.23</v>
       </c>
-      <c r="AG11" s="10">
+      <c r="AG11" s="9">
         <v>-0.76</v>
       </c>
-      <c r="AH11" s="11"/>
-      <c r="AI11" s="11"/>
-      <c r="AJ11" s="11"/>
-      <c r="AK11" s="11"/>
-      <c r="AL11" s="11"/>
-      <c r="AM11" s="11"/>
-      <c r="AN11" s="11"/>
-      <c r="AO11" s="11"/>
-      <c r="AP11" s="11"/>
-      <c r="AQ11" s="11"/>
-      <c r="AR11" s="11"/>
-      <c r="AS11" s="11"/>
-      <c r="AT11" s="11"/>
-      <c r="AU11" s="23"/>
-      <c r="AV11" s="23"/>
-      <c r="AW11" s="23"/>
-      <c r="AX11" s="23"/>
-      <c r="AY11" s="23"/>
-      <c r="AZ11" s="23"/>
-      <c r="BA11" s="23"/>
-      <c r="BB11" s="23"/>
-      <c r="BC11" s="23"/>
-      <c r="BD11" s="23"/>
-      <c r="BE11" s="23"/>
-      <c r="BF11" s="23"/>
-      <c r="BG11" s="23"/>
-      <c r="BH11" s="23"/>
-      <c r="BI11" s="23"/>
-    </row>
-    <row r="12" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="AH11" s="19"/>
+      <c r="AI11" s="19"/>
+      <c r="AJ11" s="19"/>
+      <c r="AK11" s="19"/>
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="19"/>
+      <c r="AN11" s="19"/>
+      <c r="AO11" s="19"/>
+      <c r="AP11" s="19"/>
+      <c r="AQ11" s="19"/>
+      <c r="AR11" s="19"/>
+      <c r="AS11" s="19"/>
+      <c r="AT11" s="19"/>
+      <c r="AU11" s="19"/>
+      <c r="AV11" s="19"/>
+      <c r="AW11" s="19"/>
+      <c r="AX11" s="19"/>
+      <c r="AY11" s="19"/>
+      <c r="AZ11" s="19"/>
+      <c r="BA11" s="19"/>
+      <c r="BB11" s="19"/>
+      <c r="BC11" s="19"/>
+      <c r="BD11" s="19"/>
+      <c r="BE11" s="19"/>
+      <c r="BF11" s="19"/>
+      <c r="BG11" s="19"/>
+      <c r="BH11" s="19"/>
+      <c r="BI11" s="19"/>
+    </row>
+    <row r="12" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="28">
         <v>10</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="31">
         <v>-15.9</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="30">
         <v>3.8075313807531379</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="15">
         <v>26</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="15">
         <v>1.4</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="15">
         <v>-25.4</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="15">
         <v>0.7</v>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19">
+      <c r="J12" s="15"/>
+      <c r="K12" s="15">
         <v>22.2</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="15">
         <v>24.5</v>
       </c>
-      <c r="M12" s="19">
+      <c r="M12" s="15">
         <v>19.2</v>
       </c>
-      <c r="N12" s="19">
+      <c r="N12" s="15">
         <v>19.3</v>
       </c>
-      <c r="O12" s="19">
+      <c r="O12" s="15">
         <v>23.5</v>
       </c>
-      <c r="P12" s="19">
+      <c r="P12" s="15">
         <v>7</v>
       </c>
-      <c r="Q12" s="19">
+      <c r="Q12" s="15">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R12" s="19">
+      <c r="R12" s="15">
         <v>2.2000000000000002</v>
       </c>
-      <c r="S12" s="19">
+      <c r="S12" s="15">
         <v>0.7</v>
       </c>
-      <c r="T12" s="19">
+      <c r="T12" s="15">
         <v>0.53</v>
       </c>
-      <c r="U12" s="19">
+      <c r="U12" s="15">
         <v>0.45</v>
       </c>
-      <c r="V12" s="19">
+      <c r="V12" s="15">
         <v>0.71</v>
       </c>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19">
+      <c r="W12" s="15"/>
+      <c r="X12" s="15">
         <v>0.93</v>
       </c>
-      <c r="Y12" s="19">
+      <c r="Y12" s="15">
         <v>0.42</v>
       </c>
-      <c r="Z12" s="19">
+      <c r="Z12" s="15">
         <v>0.17</v>
       </c>
-      <c r="AA12" s="19">
+      <c r="AA12" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AB12" s="19">
+      <c r="AB12" s="15">
         <v>0.19</v>
       </c>
-      <c r="AC12" s="19">
+      <c r="AC12" s="15">
         <v>0.64</v>
       </c>
-      <c r="AD12" s="19">
+      <c r="AD12" s="15">
         <v>0.34</v>
       </c>
-      <c r="AE12" s="19">
+      <c r="AE12" s="15">
         <v>0.22</v>
       </c>
-      <c r="AF12" s="10">
+      <c r="AF12" s="9">
         <v>0.42</v>
       </c>
-      <c r="AG12" s="10">
+      <c r="AG12" s="9">
         <v>0.5</v>
       </c>
-      <c r="AH12" s="11">
+      <c r="AH12" s="19">
         <v>-13.2</v>
       </c>
-      <c r="AI12" s="11">
+      <c r="AI12" s="19">
         <v>-3.4</v>
       </c>
-      <c r="AJ12" s="11">
+      <c r="AJ12" s="19">
         <v>-8.1999999999999993</v>
       </c>
-      <c r="AK12" s="11">
+      <c r="AK12" s="19">
         <v>7.3</v>
       </c>
-      <c r="AL12" s="11">
+      <c r="AL12" s="19">
         <v>-20.100000000000001</v>
       </c>
-      <c r="AM12" s="11">
+      <c r="AM12" s="19">
         <v>-22.1</v>
       </c>
-      <c r="AN12" s="11">
+      <c r="AN12" s="19">
         <v>-16.899999999999999</v>
       </c>
-      <c r="AO12" s="11">
+      <c r="AO12" s="19">
         <v>-12.2</v>
       </c>
-      <c r="AP12" s="11">
+      <c r="AP12" s="19">
         <v>-13.1</v>
       </c>
-      <c r="AQ12" s="11">
+      <c r="AQ12" s="19">
         <v>-11.6</v>
       </c>
-      <c r="AR12" s="11">
+      <c r="AR12" s="19">
         <v>-23.3</v>
       </c>
-      <c r="AS12" s="11">
+      <c r="AS12" s="19">
         <v>-23.6</v>
       </c>
-      <c r="AT12" s="11">
+      <c r="AT12" s="19">
         <v>-16.8</v>
       </c>
-      <c r="AU12" s="23">
+      <c r="AU12" s="19">
         <v>0.53</v>
       </c>
-      <c r="AV12" s="23">
+      <c r="AV12" s="19">
         <v>0.31</v>
       </c>
-      <c r="AW12" s="23">
+      <c r="AW12" s="19">
         <v>0.71</v>
       </c>
-      <c r="AX12" s="23">
+      <c r="AX12" s="19">
         <v>0.71</v>
       </c>
-      <c r="AY12" s="23">
+      <c r="AY12" s="19">
         <v>0.12</v>
       </c>
-      <c r="AZ12" s="23">
+      <c r="AZ12" s="19">
         <v>0.23</v>
       </c>
-      <c r="BA12" s="23">
+      <c r="BA12" s="19">
         <v>0.24</v>
       </c>
-      <c r="BB12" s="23">
+      <c r="BB12" s="19">
         <v>0.14000000000000001</v>
       </c>
-      <c r="BC12" s="23">
+      <c r="BC12" s="19">
         <v>0.21</v>
       </c>
-      <c r="BD12" s="23">
+      <c r="BD12" s="19">
         <v>0.37</v>
       </c>
-      <c r="BE12" s="23">
+      <c r="BE12" s="19">
         <v>0.24</v>
       </c>
-      <c r="BF12" s="23">
+      <c r="BF12" s="19">
         <v>0.61</v>
       </c>
-      <c r="BG12" s="23">
+      <c r="BG12" s="19">
         <v>0.41</v>
       </c>
-      <c r="BH12" s="23">
+      <c r="BH12" s="19">
         <v>0.37</v>
       </c>
-      <c r="BI12" s="23">
+      <c r="BI12" s="19">
         <v>0.16</v>
       </c>
     </row>
-    <row r="13" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="28">
         <v>10.3</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="31">
         <v>-15.5</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="30">
         <v>3.8609112709832134</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="15">
         <v>22.6</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="15">
         <v>0.1</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="15">
         <v>-27.8</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="15">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="15">
         <v>23.2</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="15">
         <v>20.9</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="15">
         <v>21.8</v>
       </c>
-      <c r="M13" s="19">
+      <c r="M13" s="15">
         <v>17.7</v>
       </c>
-      <c r="N13" s="19">
+      <c r="N13" s="15">
         <v>17.600000000000001</v>
       </c>
-      <c r="O13" s="19">
+      <c r="O13" s="15">
         <v>22.1</v>
       </c>
-      <c r="P13" s="19">
+      <c r="P13" s="15">
         <v>2</v>
       </c>
-      <c r="Q13" s="19">
+      <c r="Q13" s="15">
         <v>7.6</v>
       </c>
-      <c r="R13" s="19">
+      <c r="R13" s="15">
         <v>2.7</v>
       </c>
-      <c r="S13" s="19">
+      <c r="S13" s="15">
         <v>0.94</v>
       </c>
-      <c r="T13" s="19">
+      <c r="T13" s="15">
         <v>0.64</v>
       </c>
-      <c r="U13" s="19">
+      <c r="U13" s="15">
         <v>0.2</v>
       </c>
-      <c r="V13" s="19">
+      <c r="V13" s="15">
         <v>0.48</v>
       </c>
-      <c r="W13" s="19">
+      <c r="W13" s="15">
         <v>0.36</v>
       </c>
-      <c r="X13" s="19">
+      <c r="X13" s="15">
         <v>0.51</v>
       </c>
-      <c r="Y13" s="19">
+      <c r="Y13" s="15">
         <v>0.6</v>
       </c>
-      <c r="Z13" s="19">
+      <c r="Z13" s="15">
         <v>0.31</v>
       </c>
-      <c r="AA13" s="19">
+      <c r="AA13" s="15">
         <v>0.27</v>
       </c>
-      <c r="AB13" s="19">
+      <c r="AB13" s="15">
         <v>0.18</v>
       </c>
-      <c r="AC13" s="19">
+      <c r="AC13" s="15">
         <v>0.38</v>
       </c>
-      <c r="AD13" s="19">
+      <c r="AD13" s="15">
         <v>0.33</v>
       </c>
-      <c r="AE13" s="19">
+      <c r="AE13" s="15">
         <v>0.54</v>
       </c>
-      <c r="AF13" s="10">
+      <c r="AF13" s="9">
         <v>0.47</v>
       </c>
-      <c r="AG13" s="10">
+      <c r="AG13" s="9">
         <v>-0.41</v>
       </c>
-      <c r="AH13" s="11">
+      <c r="AH13" s="19">
         <v>-12.1</v>
       </c>
-      <c r="AI13" s="11">
+      <c r="AI13" s="19">
         <v>-0.7</v>
       </c>
-      <c r="AJ13" s="11">
+      <c r="AJ13" s="19">
         <v>-8.6</v>
       </c>
-      <c r="AK13" s="11">
+      <c r="AK13" s="19">
         <v>12.1</v>
       </c>
-      <c r="AL13" s="11">
+      <c r="AL13" s="19">
         <v>-19</v>
       </c>
-      <c r="AM13" s="11">
+      <c r="AM13" s="19">
         <v>-21.3</v>
       </c>
-      <c r="AN13" s="11">
+      <c r="AN13" s="19">
         <v>-16.399999999999999</v>
       </c>
-      <c r="AO13" s="11">
+      <c r="AO13" s="19">
         <v>-12.3</v>
       </c>
-      <c r="AP13" s="11">
+      <c r="AP13" s="19">
         <v>-12.2</v>
       </c>
-      <c r="AQ13" s="11">
+      <c r="AQ13" s="19">
         <v>-12.5</v>
       </c>
-      <c r="AR13" s="11">
+      <c r="AR13" s="19">
         <v>-23.2</v>
       </c>
-      <c r="AS13" s="11">
+      <c r="AS13" s="19">
         <v>-23.9</v>
       </c>
-      <c r="AT13" s="11">
+      <c r="AT13" s="19">
         <v>-14.7</v>
       </c>
-      <c r="AU13" s="23">
+      <c r="AU13" s="19">
         <v>0.27</v>
       </c>
-      <c r="AV13" s="23">
+      <c r="AV13" s="19">
         <v>0.25</v>
       </c>
-      <c r="AW13" s="23">
+      <c r="AW13" s="19">
         <v>0.33</v>
       </c>
-      <c r="AX13" s="23">
+      <c r="AX13" s="19">
         <v>0.93</v>
       </c>
-      <c r="AY13" s="23">
+      <c r="AY13" s="19">
         <v>0.18</v>
       </c>
-      <c r="AZ13" s="23">
+      <c r="AZ13" s="19">
         <v>0.25</v>
       </c>
-      <c r="BA13" s="23">
+      <c r="BA13" s="19">
         <v>0.49</v>
       </c>
-      <c r="BB13" s="23">
+      <c r="BB13" s="19">
         <v>0.52</v>
       </c>
-      <c r="BC13" s="23">
+      <c r="BC13" s="19">
         <v>0.2</v>
       </c>
-      <c r="BD13" s="23">
+      <c r="BD13" s="19">
         <v>0.4</v>
       </c>
-      <c r="BE13" s="23">
+      <c r="BE13" s="19">
         <v>0.45</v>
       </c>
-      <c r="BF13" s="23">
+      <c r="BF13" s="19">
         <v>0.82</v>
       </c>
-      <c r="BG13" s="23">
+      <c r="BG13" s="19">
         <v>0.43</v>
       </c>
-      <c r="BH13" s="23">
+      <c r="BH13" s="19">
         <v>0.4</v>
       </c>
-      <c r="BI13" s="23">
+      <c r="BI13" s="19">
         <v>0.3</v>
       </c>
     </row>
-    <row r="14" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="28">
         <v>10.4</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="31">
         <v>-17.399999999999999</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="30">
         <v>5.4817073170731705</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="15">
         <v>26.8</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="15">
         <v>2.8</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="15">
         <v>-25.1</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="15">
         <v>2.4</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="15">
         <v>16.7</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="15">
         <v>22.3</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="15">
         <v>23</v>
       </c>
-      <c r="M14" s="19">
+      <c r="M14" s="15">
         <v>19.3</v>
       </c>
-      <c r="N14" s="19">
+      <c r="N14" s="15">
         <v>19.5</v>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="15">
         <v>22.9</v>
       </c>
-      <c r="P14" s="19">
+      <c r="P14" s="15">
         <v>5.6</v>
       </c>
-      <c r="Q14" s="19">
+      <c r="Q14" s="15">
         <v>8.9</v>
       </c>
-      <c r="R14" s="19">
+      <c r="R14" s="15">
         <v>3.2</v>
       </c>
-      <c r="S14" s="19">
+      <c r="S14" s="15">
         <v>0.36</v>
       </c>
-      <c r="T14" s="19">
+      <c r="T14" s="15">
         <v>0.11</v>
       </c>
-      <c r="U14" s="19">
+      <c r="U14" s="15">
         <v>0.72</v>
       </c>
-      <c r="V14" s="19">
+      <c r="V14" s="15">
         <v>0.62</v>
       </c>
-      <c r="W14" s="19">
+      <c r="W14" s="15">
         <v>0.11</v>
       </c>
-      <c r="X14" s="19">
+      <c r="X14" s="15">
         <v>0.05</v>
       </c>
-      <c r="Y14" s="19">
+      <c r="Y14" s="15">
         <v>0.25</v>
       </c>
-      <c r="Z14" s="19">
+      <c r="Z14" s="15">
         <v>0.05</v>
       </c>
-      <c r="AA14" s="19">
+      <c r="AA14" s="15">
         <v>0.11</v>
       </c>
-      <c r="AB14" s="19">
+      <c r="AB14" s="15">
         <v>0.23</v>
       </c>
-      <c r="AC14" s="19">
+      <c r="AC14" s="15">
         <v>0.54</v>
       </c>
-      <c r="AD14" s="19">
+      <c r="AD14" s="15">
         <v>0.11</v>
       </c>
-      <c r="AE14" s="19">
+      <c r="AE14" s="15">
         <v>0.18</v>
       </c>
-      <c r="AF14" s="10">
+      <c r="AF14" s="9">
         <v>0.38</v>
       </c>
-      <c r="AG14" s="10">
+      <c r="AG14" s="9">
         <v>-0.27</v>
       </c>
-      <c r="AH14" s="11">
+      <c r="AH14" s="19">
         <v>-14.2</v>
       </c>
-      <c r="AI14" s="11">
+      <c r="AI14" s="19">
         <v>-1.7</v>
       </c>
-      <c r="AJ14" s="11">
+      <c r="AJ14" s="19">
         <v>-8.4</v>
       </c>
-      <c r="AK14" s="11">
+      <c r="AK14" s="19">
         <v>7.5</v>
       </c>
-      <c r="AL14" s="11">
+      <c r="AL14" s="19">
         <v>-19.2</v>
       </c>
-      <c r="AM14" s="11">
+      <c r="AM14" s="19">
         <v>-21.5</v>
       </c>
-      <c r="AN14" s="11">
+      <c r="AN14" s="19">
         <v>-17.100000000000001</v>
       </c>
-      <c r="AO14" s="11">
+      <c r="AO14" s="19">
         <v>-12.3</v>
       </c>
-      <c r="AP14" s="11">
+      <c r="AP14" s="19">
         <v>-13.2</v>
       </c>
-      <c r="AQ14" s="11">
+      <c r="AQ14" s="19">
         <v>-13.1</v>
       </c>
-      <c r="AR14" s="11">
+      <c r="AR14" s="19">
         <v>-20.3</v>
       </c>
-      <c r="AS14" s="11">
+      <c r="AS14" s="19">
         <v>-21.9</v>
       </c>
-      <c r="AT14" s="11">
+      <c r="AT14" s="19">
         <v>-17.100000000000001</v>
       </c>
-      <c r="AU14" s="23">
+      <c r="AU14" s="19">
         <v>0.45</v>
       </c>
-      <c r="AV14" s="23">
+      <c r="AV14" s="19">
         <v>0.41</v>
       </c>
-      <c r="AW14" s="23">
+      <c r="AW14" s="19">
         <v>0.24</v>
       </c>
-      <c r="AX14" s="23">
+      <c r="AX14" s="19">
         <v>0.56000000000000005</v>
       </c>
-      <c r="AY14" s="23">
+      <c r="AY14" s="19">
         <v>0.9</v>
       </c>
-      <c r="AZ14" s="23">
+      <c r="AZ14" s="19">
         <v>0.3</v>
       </c>
-      <c r="BA14" s="23">
+      <c r="BA14" s="19">
         <v>0.64</v>
       </c>
-      <c r="BB14" s="23">
+      <c r="BB14" s="19">
         <v>0.2</v>
       </c>
-      <c r="BC14" s="23">
+      <c r="BC14" s="19">
         <v>0.19</v>
       </c>
-      <c r="BD14" s="23">
+      <c r="BD14" s="19">
         <v>0.24</v>
       </c>
-      <c r="BE14" s="23">
+      <c r="BE14" s="19">
         <v>0.45</v>
       </c>
-      <c r="BF14" s="23">
+      <c r="BF14" s="19">
         <v>0.17</v>
       </c>
-      <c r="BG14" s="23">
+      <c r="BG14" s="19">
         <v>0.45</v>
       </c>
-      <c r="BH14" s="23">
+      <c r="BH14" s="19">
         <v>0.39</v>
       </c>
-      <c r="BI14" s="23">
+      <c r="BI14" s="19">
         <v>0.26</v>
       </c>
     </row>
-    <row r="15" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="28">
         <v>10.7</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="31">
         <v>-15</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="30">
         <v>3.7313043478260877</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="15">
         <v>28</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="15">
         <v>2</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="15">
         <v>-24.2</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="15">
         <v>-2.4</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="15">
         <v>23.7</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="15">
         <v>23.5</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="15">
         <v>24.9</v>
       </c>
-      <c r="M15" s="19">
+      <c r="M15" s="15">
         <v>20.399999999999999</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="15">
         <v>20.7</v>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="15">
         <v>24.6</v>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="15">
         <v>7</v>
       </c>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19">
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15">
         <v>3.2</v>
       </c>
-      <c r="S15" s="19">
+      <c r="S15" s="15">
         <v>0.28000000000000003</v>
       </c>
-      <c r="T15" s="19">
+      <c r="T15" s="15">
         <v>0.64</v>
       </c>
-      <c r="U15" s="19">
+      <c r="U15" s="15">
         <v>0.56999999999999995</v>
       </c>
-      <c r="V15" s="19">
+      <c r="V15" s="15">
         <v>0.89</v>
       </c>
-      <c r="W15" s="19">
+      <c r="W15" s="15">
         <v>0.71</v>
       </c>
-      <c r="X15" s="19">
+      <c r="X15" s="15">
         <v>0.48</v>
       </c>
-      <c r="Y15" s="19">
+      <c r="Y15" s="15">
         <v>0.66</v>
       </c>
-      <c r="Z15" s="19">
+      <c r="Z15" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AA15" s="19">
+      <c r="AA15" s="15">
         <v>0.34</v>
       </c>
-      <c r="AB15" s="19">
+      <c r="AB15" s="15">
         <v>0.32</v>
       </c>
-      <c r="AC15" s="19">
+      <c r="AC15" s="15">
         <v>0.62</v>
       </c>
-      <c r="AD15" s="19"/>
-      <c r="AE15" s="19">
+      <c r="AD15" s="15"/>
+      <c r="AE15" s="15">
         <v>0.32</v>
       </c>
-      <c r="AF15" s="10">
+      <c r="AF15" s="9">
         <v>0.88</v>
       </c>
-      <c r="AG15" s="10">
+      <c r="AG15" s="9">
         <v>-0.81</v>
       </c>
-      <c r="AH15" s="11">
+      <c r="AH15" s="19">
         <v>-12.1</v>
       </c>
-      <c r="AI15" s="11">
+      <c r="AI15" s="19">
         <v>-1.2</v>
       </c>
-      <c r="AJ15" s="11">
+      <c r="AJ15" s="19">
         <v>-9</v>
       </c>
-      <c r="AK15" s="11">
+      <c r="AK15" s="19">
         <v>8.5</v>
       </c>
-      <c r="AL15" s="11">
+      <c r="AL15" s="19">
         <v>-19.899999999999999</v>
       </c>
-      <c r="AM15" s="11">
+      <c r="AM15" s="19">
         <v>-21.5</v>
       </c>
-      <c r="AN15" s="11">
+      <c r="AN15" s="19">
         <v>-16.8</v>
       </c>
-      <c r="AO15" s="11">
+      <c r="AO15" s="19">
         <v>-12.4</v>
       </c>
-      <c r="AP15" s="11">
+      <c r="AP15" s="19">
         <v>-12.9</v>
       </c>
-      <c r="AQ15" s="11">
+      <c r="AQ15" s="19">
         <v>-12</v>
       </c>
-      <c r="AR15" s="11">
+      <c r="AR15" s="19">
         <v>-20.399999999999999</v>
       </c>
-      <c r="AS15" s="11">
+      <c r="AS15" s="19">
         <v>-20.9</v>
       </c>
-      <c r="AT15" s="11">
+      <c r="AT15" s="19">
         <v>-17.3</v>
       </c>
-      <c r="AU15" s="23">
+      <c r="AU15" s="19">
         <v>0.16</v>
       </c>
-      <c r="AV15" s="23">
+      <c r="AV15" s="19">
         <v>0.28000000000000003</v>
       </c>
-      <c r="AW15" s="23">
+      <c r="AW15" s="19">
         <v>0.97</v>
       </c>
-      <c r="AX15" s="23">
+      <c r="AX15" s="19">
         <v>1.08</v>
       </c>
-      <c r="AY15" s="23">
+      <c r="AY15" s="19">
         <v>0.3</v>
       </c>
-      <c r="AZ15" s="23">
+      <c r="AZ15" s="19">
         <v>0.41</v>
       </c>
-      <c r="BA15" s="23">
+      <c r="BA15" s="19">
         <v>0.95</v>
       </c>
-      <c r="BB15" s="23">
+      <c r="BB15" s="19">
         <v>0.1</v>
       </c>
-      <c r="BC15" s="23">
+      <c r="BC15" s="19">
         <v>0.6</v>
       </c>
-      <c r="BD15" s="23">
+      <c r="BD15" s="19">
         <v>0.1</v>
       </c>
-      <c r="BE15" s="23">
+      <c r="BE15" s="19">
         <v>0.93</v>
       </c>
-      <c r="BF15" s="23">
+      <c r="BF15" s="19">
         <v>0.39</v>
       </c>
-      <c r="BG15" s="23">
+      <c r="BG15" s="19">
         <v>0.04</v>
       </c>
-      <c r="BH15" s="23">
+      <c r="BH15" s="19">
         <v>0.5</v>
       </c>
-      <c r="BI15" s="23">
+      <c r="BI15" s="19">
         <v>0.62</v>
       </c>
     </row>
-    <row r="16" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="28">
         <v>9.9</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="31">
         <v>-14.9</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="30">
         <v>3.7800882167611847</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="15">
         <v>25.9</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="15">
         <v>2.7</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="15">
         <v>-25.3</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="15">
         <v>3</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="15">
         <v>25.8</v>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="15">
         <v>23.6</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="15">
         <v>24.7</v>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="15">
         <v>18.7</v>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="15">
         <v>18.399999999999999</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="15">
         <v>23.1</v>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="15">
         <v>2</v>
       </c>
-      <c r="Q16" s="19">
+      <c r="Q16" s="15">
         <v>10.3</v>
       </c>
-      <c r="R16" s="19">
+      <c r="R16" s="15">
         <v>3.2</v>
       </c>
-      <c r="S16" s="19">
+      <c r="S16" s="15">
         <v>0.57999999999999996</v>
       </c>
-      <c r="T16" s="19">
+      <c r="T16" s="15">
         <v>0.68</v>
       </c>
-      <c r="U16" s="19">
+      <c r="U16" s="15">
         <v>0.89</v>
       </c>
-      <c r="V16" s="19">
+      <c r="V16" s="15">
         <v>0.08</v>
       </c>
-      <c r="W16" s="19">
+      <c r="W16" s="15">
         <v>0.91</v>
       </c>
-      <c r="X16" s="19">
+      <c r="X16" s="15">
         <v>0.13</v>
       </c>
-      <c r="Y16" s="19">
+      <c r="Y16" s="15">
         <v>0.24</v>
       </c>
-      <c r="Z16" s="19">
+      <c r="Z16" s="15">
         <v>0.31</v>
       </c>
-      <c r="AA16" s="19">
+      <c r="AA16" s="15">
         <v>0.32</v>
       </c>
-      <c r="AB16" s="19">
+      <c r="AB16" s="15">
         <v>0.08</v>
       </c>
-      <c r="AC16" s="19">
+      <c r="AC16" s="15">
         <v>0.7</v>
       </c>
-      <c r="AD16" s="19">
+      <c r="AD16" s="15">
         <v>0.24</v>
       </c>
-      <c r="AE16" s="19">
+      <c r="AE16" s="15">
         <v>0.31</v>
       </c>
-      <c r="AF16" s="10">
+      <c r="AF16" s="9">
         <v>0.8</v>
       </c>
-      <c r="AG16" s="10">
+      <c r="AG16" s="9">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="AH16" s="11">
+      <c r="AH16" s="19">
         <v>-12.7</v>
       </c>
-      <c r="AI16" s="11">
+      <c r="AI16" s="19">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="AJ16" s="11">
+      <c r="AJ16" s="19">
         <v>-9.3000000000000007</v>
       </c>
-      <c r="AK16" s="11">
+      <c r="AK16" s="19">
         <v>4.5</v>
       </c>
-      <c r="AL16" s="11">
+      <c r="AL16" s="19">
         <v>-18.5</v>
       </c>
-      <c r="AM16" s="11">
+      <c r="AM16" s="19">
         <v>-20.9</v>
       </c>
-      <c r="AN16" s="11">
+      <c r="AN16" s="19">
         <v>-17</v>
       </c>
-      <c r="AO16" s="11">
+      <c r="AO16" s="19">
         <v>-11.7</v>
       </c>
-      <c r="AP16" s="11">
+      <c r="AP16" s="19">
         <v>-12</v>
       </c>
-      <c r="AQ16" s="11">
+      <c r="AQ16" s="19">
         <v>-10.9</v>
       </c>
-      <c r="AR16" s="11">
+      <c r="AR16" s="19">
         <v>-20</v>
       </c>
-      <c r="AS16" s="11">
+      <c r="AS16" s="19">
         <v>-20.5</v>
       </c>
-      <c r="AT16" s="11">
+      <c r="AT16" s="19">
         <v>-17.100000000000001</v>
       </c>
-      <c r="AU16" s="23">
+      <c r="AU16" s="19">
         <v>0.47</v>
       </c>
-      <c r="AV16" s="23">
+      <c r="AV16" s="19">
         <v>0.45</v>
       </c>
-      <c r="AW16" s="23">
+      <c r="AW16" s="19">
         <v>0.74</v>
       </c>
-      <c r="AX16" s="23">
+      <c r="AX16" s="19">
         <v>0.9</v>
       </c>
-      <c r="AY16" s="23">
+      <c r="AY16" s="19">
         <v>0.85</v>
       </c>
-      <c r="AZ16" s="23">
+      <c r="AZ16" s="19">
         <v>0.1</v>
       </c>
-      <c r="BA16" s="23">
+      <c r="BA16" s="19">
         <v>0.7</v>
       </c>
-      <c r="BB16" s="23">
+      <c r="BB16" s="19">
         <v>0.19</v>
       </c>
-      <c r="BC16" s="23">
+      <c r="BC16" s="19">
         <v>0.32</v>
       </c>
-      <c r="BD16" s="23">
+      <c r="BD16" s="19">
         <v>0.34</v>
       </c>
-      <c r="BE16" s="23">
+      <c r="BE16" s="19">
         <v>0.96</v>
       </c>
-      <c r="BF16" s="23">
+      <c r="BF16" s="19">
         <v>0.33</v>
       </c>
-      <c r="BG16" s="23">
+      <c r="BG16" s="19">
         <v>0.3</v>
       </c>
-      <c r="BH16" s="23">
+      <c r="BH16" s="19">
         <v>0.46</v>
       </c>
-      <c r="BI16" s="23">
+      <c r="BI16" s="19">
         <v>0.19</v>
       </c>
     </row>
-    <row r="17" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="28">
         <v>10.1</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="31">
         <v>-15.4</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="30">
         <v>3.2807146353401864</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="15">
         <v>21.1</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="15">
         <v>0.6</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="15">
         <v>-26.6</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="15">
         <v>-1.5</v>
       </c>
-      <c r="J17" s="19">
+      <c r="J17" s="15">
         <v>20.8</v>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="15">
         <v>20.100000000000001</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="15">
         <v>21.3</v>
       </c>
-      <c r="M17" s="19">
+      <c r="M17" s="15">
         <v>14.8</v>
       </c>
-      <c r="N17" s="19">
+      <c r="N17" s="15">
         <v>16.600000000000001</v>
       </c>
-      <c r="O17" s="19">
+      <c r="O17" s="15">
         <v>22.1</v>
       </c>
-      <c r="P17" s="19">
+      <c r="P17" s="15">
         <v>3.3</v>
       </c>
-      <c r="Q17" s="19">
+      <c r="Q17" s="15">
         <v>9</v>
       </c>
-      <c r="R17" s="19">
+      <c r="R17" s="15">
         <v>1.9</v>
       </c>
-      <c r="S17" s="19">
+      <c r="S17" s="15">
         <v>0.15</v>
       </c>
-      <c r="T17" s="19">
+      <c r="T17" s="15">
         <v>0.16</v>
       </c>
-      <c r="U17" s="19">
+      <c r="U17" s="15">
         <v>0.4</v>
       </c>
-      <c r="V17" s="19">
+      <c r="V17" s="15">
         <v>0.97</v>
       </c>
-      <c r="W17" s="19">
+      <c r="W17" s="15">
         <v>0.67</v>
       </c>
-      <c r="X17" s="19">
+      <c r="X17" s="15">
         <v>0.09</v>
       </c>
-      <c r="Y17" s="19">
+      <c r="Y17" s="15">
         <v>0.39</v>
       </c>
-      <c r="Z17" s="19">
+      <c r="Z17" s="15">
         <v>0.18</v>
       </c>
-      <c r="AA17" s="19">
+      <c r="AA17" s="15">
         <v>0.19</v>
       </c>
-      <c r="AB17" s="19">
+      <c r="AB17" s="15">
         <v>0.15</v>
       </c>
-      <c r="AC17" s="19">
+      <c r="AC17" s="15">
         <v>0.42</v>
       </c>
-      <c r="AD17" s="19">
+      <c r="AD17" s="15">
         <v>0.33</v>
       </c>
-      <c r="AE17" s="19">
+      <c r="AE17" s="15">
         <v>0.2</v>
       </c>
-      <c r="AF17" s="10">
+      <c r="AF17" s="9">
         <v>0.38</v>
       </c>
-      <c r="AG17" s="10">
+      <c r="AG17" s="9">
         <v>0.76</v>
       </c>
-      <c r="AH17" s="11">
+      <c r="AH17" s="19">
         <v>-12.6</v>
       </c>
-      <c r="AI17" s="11">
+      <c r="AI17" s="19">
         <v>-1.3</v>
       </c>
-      <c r="AJ17" s="11">
+      <c r="AJ17" s="19">
         <v>-8.1</v>
       </c>
-      <c r="AK17" s="11">
+      <c r="AK17" s="19">
         <v>5.6</v>
       </c>
-      <c r="AL17" s="11">
+      <c r="AL17" s="19">
         <v>-19.2</v>
       </c>
-      <c r="AM17" s="11">
+      <c r="AM17" s="19">
         <v>-21.4</v>
       </c>
-      <c r="AN17" s="11">
+      <c r="AN17" s="19">
         <v>-16.5</v>
       </c>
-      <c r="AO17" s="11">
+      <c r="AO17" s="19">
         <v>-13.1</v>
       </c>
-      <c r="AP17" s="11">
+      <c r="AP17" s="19">
         <v>-12.1</v>
       </c>
-      <c r="AQ17" s="11">
+      <c r="AQ17" s="19">
         <v>-11.3</v>
       </c>
-      <c r="AR17" s="11">
+      <c r="AR17" s="19">
         <v>-19.8</v>
       </c>
-      <c r="AS17" s="11">
+      <c r="AS17" s="19">
         <v>-20.3</v>
       </c>
-      <c r="AT17" s="11">
+      <c r="AT17" s="19">
         <v>-17.5</v>
       </c>
-      <c r="AU17" s="23">
+      <c r="AU17" s="19">
         <v>0.44</v>
       </c>
-      <c r="AV17" s="23">
+      <c r="AV17" s="19">
         <v>0.45</v>
       </c>
-      <c r="AW17" s="23">
+      <c r="AW17" s="19">
         <v>0.16</v>
       </c>
-      <c r="AX17" s="23">
+      <c r="AX17" s="19">
         <v>0.78</v>
       </c>
-      <c r="AY17" s="23">
+      <c r="AY17" s="19">
         <v>0.34</v>
       </c>
-      <c r="AZ17" s="23">
+      <c r="AZ17" s="19">
         <v>0.13</v>
       </c>
-      <c r="BA17" s="23">
+      <c r="BA17" s="19">
         <v>0.27</v>
       </c>
-      <c r="BB17" s="23">
+      <c r="BB17" s="19">
         <v>0.56999999999999995</v>
       </c>
-      <c r="BC17" s="23">
+      <c r="BC17" s="19">
         <v>0.38</v>
       </c>
-      <c r="BD17" s="23">
+      <c r="BD17" s="19">
         <v>0.76</v>
       </c>
-      <c r="BE17" s="23">
+      <c r="BE17" s="19">
         <v>0.99</v>
       </c>
-      <c r="BF17" s="23">
+      <c r="BF17" s="19">
         <v>0.43</v>
       </c>
-      <c r="BG17" s="23">
+      <c r="BG17" s="19">
         <v>0.77</v>
       </c>
-      <c r="BH17" s="23">
+      <c r="BH17" s="19">
         <v>0.48</v>
       </c>
-      <c r="BI17" s="23">
+      <c r="BI17" s="19">
         <v>0.89</v>
       </c>
     </row>
-    <row r="18" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="28">
         <v>9.4</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="31">
         <v>-15.3</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="30">
         <v>3.151041666666667</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="15">
         <v>23.1</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="15">
         <v>-0.2</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="15">
         <v>-24.3</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="15">
         <v>2.7</v>
       </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19">
+      <c r="J18" s="15"/>
+      <c r="K18" s="15">
         <v>22.1</v>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="15">
         <v>23.4</v>
       </c>
-      <c r="M18" s="19">
+      <c r="M18" s="15">
         <v>15.2</v>
       </c>
-      <c r="N18" s="19">
+      <c r="N18" s="15">
         <v>17</v>
       </c>
-      <c r="O18" s="19">
+      <c r="O18" s="15">
         <v>22.3</v>
       </c>
-      <c r="P18" s="19">
+      <c r="P18" s="15">
         <v>1.9</v>
       </c>
-      <c r="Q18" s="19">
+      <c r="Q18" s="15">
         <v>9.3000000000000007</v>
       </c>
-      <c r="R18" s="19">
+      <c r="R18" s="15">
         <v>1.7</v>
       </c>
-      <c r="S18" s="19">
+      <c r="S18" s="15">
         <v>0.42</v>
       </c>
-      <c r="T18" s="19">
+      <c r="T18" s="15">
         <v>0.5</v>
       </c>
-      <c r="U18" s="19">
+      <c r="U18" s="15">
         <v>0.95</v>
       </c>
-      <c r="V18" s="19">
+      <c r="V18" s="15">
         <v>0.6</v>
       </c>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19">
+      <c r="W18" s="15"/>
+      <c r="X18" s="15">
         <v>0.68</v>
       </c>
-      <c r="Y18" s="19">
+      <c r="Y18" s="15">
         <v>1.03</v>
       </c>
-      <c r="Z18" s="19">
+      <c r="Z18" s="15">
         <v>0.64</v>
       </c>
-      <c r="AA18" s="19">
+      <c r="AA18" s="15">
         <v>0.75</v>
       </c>
-      <c r="AB18" s="19">
+      <c r="AB18" s="15">
         <v>0.78</v>
       </c>
-      <c r="AC18" s="19">
+      <c r="AC18" s="15">
         <v>0.02</v>
       </c>
-      <c r="AD18" s="19">
+      <c r="AD18" s="15">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AE18" s="19">
+      <c r="AE18" s="15">
         <v>1.06</v>
       </c>
-      <c r="AF18" s="10">
+      <c r="AF18" s="9">
         <v>0.77</v>
       </c>
-      <c r="AG18" s="10">
+      <c r="AG18" s="9">
         <v>0.9</v>
       </c>
-      <c r="AH18" s="11">
+      <c r="AH18" s="19">
         <v>-12.5</v>
       </c>
-      <c r="AI18" s="11">
+      <c r="AI18" s="19">
         <v>-6.9</v>
       </c>
-      <c r="AJ18" s="11">
+      <c r="AJ18" s="19">
         <v>-7.7</v>
       </c>
-      <c r="AK18" s="11">
+      <c r="AK18" s="19">
         <v>7.5</v>
       </c>
-      <c r="AL18" s="11">
+      <c r="AL18" s="19">
         <v>-17.5</v>
       </c>
-      <c r="AM18" s="11">
+      <c r="AM18" s="19">
         <v>-21.6</v>
       </c>
-      <c r="AN18" s="11">
+      <c r="AN18" s="19">
         <v>-15.9</v>
       </c>
-      <c r="AO18" s="11">
+      <c r="AO18" s="19">
         <v>-13</v>
       </c>
-      <c r="AP18" s="11">
+      <c r="AP18" s="19">
         <v>-10.9</v>
       </c>
-      <c r="AQ18" s="11">
+      <c r="AQ18" s="19">
         <v>-10.4</v>
       </c>
-      <c r="AR18" s="11">
+      <c r="AR18" s="19">
         <v>-21.2</v>
       </c>
-      <c r="AS18" s="11">
+      <c r="AS18" s="19">
         <v>-23.5</v>
       </c>
-      <c r="AT18" s="11">
+      <c r="AT18" s="19">
         <v>-15.8</v>
       </c>
-      <c r="AU18" s="23">
+      <c r="AU18" s="19">
         <v>0.73</v>
       </c>
-      <c r="AV18" s="23">
+      <c r="AV18" s="19">
         <v>0.73</v>
       </c>
-      <c r="AW18" s="23">
+      <c r="AW18" s="19">
         <v>0.62</v>
       </c>
-      <c r="AX18" s="23">
+      <c r="AX18" s="19">
         <v>0.37</v>
       </c>
-      <c r="AY18" s="23">
+      <c r="AY18" s="19">
         <v>0.39</v>
       </c>
-      <c r="AZ18" s="23">
+      <c r="AZ18" s="19">
         <v>0.44</v>
       </c>
-      <c r="BA18" s="23">
+      <c r="BA18" s="19">
         <v>0.59</v>
       </c>
-      <c r="BB18" s="23">
+      <c r="BB18" s="19">
         <v>0.28000000000000003</v>
       </c>
-      <c r="BC18" s="23">
+      <c r="BC18" s="19">
         <v>0.1</v>
       </c>
-      <c r="BD18" s="23">
+      <c r="BD18" s="19">
         <v>0.28999999999999998</v>
       </c>
-      <c r="BE18" s="23">
+      <c r="BE18" s="19">
         <v>0.26</v>
       </c>
-      <c r="BF18" s="23">
+      <c r="BF18" s="19">
         <v>0.76</v>
       </c>
-      <c r="BG18" s="23">
+      <c r="BG18" s="19">
         <v>0.37</v>
       </c>
-      <c r="BH18" s="23">
+      <c r="BH18" s="19">
         <v>0.42</v>
       </c>
-      <c r="BI18" s="23">
+      <c r="BI18" s="19">
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="28">
         <v>10</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="31">
         <v>-14.1</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="30">
         <v>3.2562862669245649</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="15">
         <v>25.9</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="15">
         <v>4.7</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="15">
         <v>-27.1</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="15">
         <v>3.2</v>
       </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19">
+      <c r="J19" s="15"/>
+      <c r="K19" s="15">
         <v>24.5</v>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="15">
         <v>25.6</v>
       </c>
-      <c r="M19" s="19">
+      <c r="M19" s="15">
         <v>16.3</v>
       </c>
-      <c r="N19" s="19">
+      <c r="N19" s="15">
         <v>18.899999999999999</v>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="15">
         <v>24.7</v>
       </c>
-      <c r="P19" s="19">
+      <c r="P19" s="15">
         <v>3.2</v>
       </c>
-      <c r="Q19" s="19">
+      <c r="Q19" s="15">
         <v>12</v>
       </c>
-      <c r="R19" s="19">
+      <c r="R19" s="15">
         <v>3.3</v>
       </c>
-      <c r="S19" s="19">
+      <c r="S19" s="15">
         <v>0.2</v>
       </c>
-      <c r="T19" s="19">
+      <c r="T19" s="15">
         <v>0.12</v>
       </c>
-      <c r="U19" s="19">
+      <c r="U19" s="15">
         <v>0.18</v>
       </c>
-      <c r="V19" s="19">
+      <c r="V19" s="15">
         <v>0.33</v>
       </c>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19">
+      <c r="W19" s="15"/>
+      <c r="X19" s="15">
         <v>0.36</v>
       </c>
-      <c r="Y19" s="19">
+      <c r="Y19" s="15">
         <v>0.87</v>
       </c>
-      <c r="Z19" s="19">
+      <c r="Z19" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AA19" s="19">
+      <c r="AA19" s="15">
         <v>0.1</v>
       </c>
-      <c r="AB19" s="19">
+      <c r="AB19" s="15">
         <v>0.27</v>
       </c>
-      <c r="AC19" s="19">
+      <c r="AC19" s="15">
         <v>0.13</v>
       </c>
-      <c r="AD19" s="19">
+      <c r="AD19" s="15">
         <v>0.61</v>
       </c>
-      <c r="AE19" s="19">
+      <c r="AE19" s="15">
         <v>0.11</v>
       </c>
-      <c r="AF19" s="10">
+      <c r="AF19" s="9">
         <v>0.3</v>
       </c>
-      <c r="AG19" s="10">
+      <c r="AG19" s="9">
         <v>-0.8</v>
       </c>
-      <c r="AH19" s="11">
+      <c r="AH19" s="19">
         <v>-11.1</v>
       </c>
-      <c r="AI19" s="11">
+      <c r="AI19" s="19">
         <v>-5</v>
       </c>
-      <c r="AJ19" s="11">
+      <c r="AJ19" s="19">
         <v>-6.6</v>
       </c>
-      <c r="AK19" s="11">
+      <c r="AK19" s="19">
         <v>8.9</v>
       </c>
-      <c r="AL19" s="11">
+      <c r="AL19" s="19">
         <v>-16.100000000000001</v>
       </c>
-      <c r="AM19" s="11">
+      <c r="AM19" s="19">
         <v>-20.6</v>
       </c>
-      <c r="AN19" s="11">
+      <c r="AN19" s="19">
         <v>-15.6</v>
       </c>
-      <c r="AO19" s="11">
+      <c r="AO19" s="19">
         <v>-12.9</v>
       </c>
-      <c r="AP19" s="11">
+      <c r="AP19" s="19">
         <v>-11.9</v>
       </c>
-      <c r="AQ19" s="11">
+      <c r="AQ19" s="19">
         <v>-10.1</v>
       </c>
-      <c r="AR19" s="11">
+      <c r="AR19" s="19">
         <v>-21.3</v>
       </c>
-      <c r="AS19" s="11">
+      <c r="AS19" s="19">
         <v>-21.8</v>
       </c>
-      <c r="AT19" s="11">
+      <c r="AT19" s="19">
         <v>-14.8</v>
       </c>
-      <c r="AU19" s="23">
+      <c r="AU19" s="19">
         <v>0.44</v>
       </c>
-      <c r="AV19" s="23">
+      <c r="AV19" s="19">
         <v>0.21</v>
       </c>
-      <c r="AW19" s="23">
+      <c r="AW19" s="19">
         <v>0.85</v>
       </c>
-      <c r="AX19" s="23">
+      <c r="AX19" s="19">
         <v>0.62</v>
       </c>
-      <c r="AY19" s="23">
+      <c r="AY19" s="19">
         <v>0.72</v>
       </c>
-      <c r="AZ19" s="23">
+      <c r="AZ19" s="19">
         <v>0.37</v>
       </c>
-      <c r="BA19" s="23">
+      <c r="BA19" s="19">
         <v>0.54</v>
       </c>
-      <c r="BB19" s="23">
+      <c r="BB19" s="19">
         <v>0.2</v>
       </c>
-      <c r="BC19" s="23">
+      <c r="BC19" s="19">
         <v>0.12</v>
       </c>
-      <c r="BD19" s="23">
+      <c r="BD19" s="19">
         <v>0.38</v>
       </c>
-      <c r="BE19" s="23">
+      <c r="BE19" s="19">
         <v>0.09</v>
       </c>
-      <c r="BF19" s="23">
+      <c r="BF19" s="19">
         <v>0.62</v>
       </c>
-      <c r="BG19" s="23">
+      <c r="BG19" s="19">
         <v>0.44</v>
       </c>
-      <c r="BH19" s="23">
+      <c r="BH19" s="19">
         <v>0.4</v>
       </c>
-      <c r="BI19" s="23">
+      <c r="BI19" s="19">
         <v>0.23</v>
       </c>
     </row>
-    <row r="20" spans="1:61" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:61" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="28">
         <v>9.6</v>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="31">
         <v>-14.5</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="30">
         <v>3.1901709401709408</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="15">
         <v>24.8</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="15">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="15">
         <v>-30.7</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="15">
         <v>1.4</v>
       </c>
-      <c r="J20" s="19">
+      <c r="J20" s="15">
         <v>15.5</v>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="15">
         <v>23.8</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="15">
         <v>24.5</v>
       </c>
-      <c r="M20" s="19">
+      <c r="M20" s="15">
         <v>16.8</v>
       </c>
-      <c r="N20" s="19">
+      <c r="N20" s="15">
         <v>19.100000000000001</v>
       </c>
-      <c r="O20" s="19">
+      <c r="O20" s="15">
         <v>25.1</v>
       </c>
-      <c r="P20" s="19">
+      <c r="P20" s="15">
         <v>5.6</v>
       </c>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19">
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15">
         <v>1.5</v>
       </c>
-      <c r="S20" s="19">
+      <c r="S20" s="15">
         <v>0.18</v>
       </c>
-      <c r="T20" s="19">
+      <c r="T20" s="15">
         <v>0.23</v>
       </c>
-      <c r="U20" s="19">
+      <c r="U20" s="15">
         <v>0.2</v>
       </c>
-      <c r="V20" s="19">
+      <c r="V20" s="15">
         <v>0.33</v>
       </c>
-      <c r="W20" s="19">
+      <c r="W20" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="X20" s="19">
+      <c r="X20" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Y20" s="19">
+      <c r="Y20" s="15">
         <v>0.45</v>
       </c>
-      <c r="Z20" s="19">
+      <c r="Z20" s="15">
         <v>0.05</v>
       </c>
-      <c r="AA20" s="19">
+      <c r="AA20" s="15">
         <v>0.15</v>
       </c>
-      <c r="AB20" s="19">
+      <c r="AB20" s="15">
         <v>0.21</v>
       </c>
-      <c r="AC20" s="19">
+      <c r="AC20" s="15">
         <v>0.33</v>
       </c>
-      <c r="AD20" s="19"/>
-      <c r="AE20" s="19">
+      <c r="AD20" s="15"/>
+      <c r="AE20" s="15">
         <v>0.1</v>
       </c>
-      <c r="AF20" s="10">
+      <c r="AF20" s="9">
         <v>0.26</v>
       </c>
-      <c r="AG20" s="10">
+      <c r="AG20" s="9">
         <v>-0.84</v>
       </c>
-      <c r="AH20" s="11">
+      <c r="AH20" s="19">
         <v>-11.6</v>
       </c>
-      <c r="AI20" s="11">
+      <c r="AI20" s="19">
         <v>-4.2</v>
       </c>
-      <c r="AJ20" s="11">
+      <c r="AJ20" s="19">
         <v>-8.1999999999999993</v>
       </c>
-      <c r="AK20" s="11">
+      <c r="AK20" s="19">
         <v>7.5</v>
       </c>
-      <c r="AL20" s="11">
+      <c r="AL20" s="19">
         <v>-17.399999999999999</v>
       </c>
-      <c r="AM20" s="11">
+      <c r="AM20" s="19">
         <v>-21</v>
       </c>
-      <c r="AN20" s="11">
+      <c r="AN20" s="19">
         <v>-16.2</v>
       </c>
-      <c r="AO20" s="11">
+      <c r="AO20" s="19">
         <v>-12.5</v>
       </c>
-      <c r="AP20" s="11">
+      <c r="AP20" s="19">
         <v>-12.2</v>
       </c>
-      <c r="AQ20" s="11">
+      <c r="AQ20" s="19">
         <v>-11.1</v>
       </c>
-      <c r="AR20" s="11">
+      <c r="AR20" s="19">
         <v>-19.5</v>
       </c>
-      <c r="AS20" s="11">
+      <c r="AS20" s="19">
         <v>-20.8</v>
       </c>
-      <c r="AT20" s="11">
+      <c r="AT20" s="19">
         <v>-16.600000000000001</v>
       </c>
-      <c r="AU20" s="23">
+      <c r="AU20" s="19">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AV20" s="23">
+      <c r="AV20" s="19">
         <v>0.11</v>
       </c>
-      <c r="AW20" s="23">
+      <c r="AW20" s="19">
         <v>0.11</v>
       </c>
-      <c r="AX20" s="23">
+      <c r="AX20" s="19">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AY20" s="23">
+      <c r="AY20" s="19">
         <v>0.45</v>
       </c>
-      <c r="AZ20" s="23">
+      <c r="AZ20" s="19">
         <v>0.06</v>
       </c>
-      <c r="BA20" s="23">
+      <c r="BA20" s="19">
         <v>0.2</v>
       </c>
-      <c r="BB20" s="23">
+      <c r="BB20" s="19">
         <v>0.04</v>
       </c>
-      <c r="BC20" s="23">
+      <c r="BC20" s="19">
         <v>0.25</v>
       </c>
-      <c r="BD20" s="23">
+      <c r="BD20" s="19">
         <v>0.52</v>
       </c>
-      <c r="BE20" s="23">
+      <c r="BE20" s="19">
         <v>0.82</v>
       </c>
-      <c r="BF20" s="23">
+      <c r="BF20" s="19">
         <v>0.8</v>
       </c>
-      <c r="BG20" s="23">
+      <c r="BG20" s="19">
         <v>0.44</v>
       </c>
-      <c r="BH20" s="23">
+      <c r="BH20" s="19">
         <v>0.38</v>
       </c>
-      <c r="BI20" s="23">
+      <c r="BI20" s="19">
         <v>0.36</v>
       </c>
     </row>
@@ -5573,6 +5605,7 @@
     <mergeCell ref="AU1:BG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5581,14 +5614,14 @@
   <dimension ref="A1:AG21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="31" width="7.42578125" style="31" customWidth="1"/>
-    <col min="32" max="32" width="9.140625" style="31"/>
-    <col min="33" max="33" width="8.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="31" width="7.42578125" style="27" customWidth="1"/>
+    <col min="32" max="32" width="9.140625" style="27"/>
+    <col min="33" max="33" width="8.7109375" style="27" bestFit="1" customWidth="1"/>
     <col min="226" max="226" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="227" max="227" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="228" max="228" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -6852,1947 +6885,2061 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="1" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="25"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="13" t="s">
+      <c r="A1" s="21"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="13" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="26"/>
-    </row>
-    <row r="2" spans="1:33" s="24" customFormat="1" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="A2" s="27" t="s">
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="21"/>
+      <c r="AG1" s="22"/>
+    </row>
+    <row r="2" spans="1:33" s="20" customFormat="1" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="N2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="27" t="s">
+      <c r="P2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="27" t="s">
+      <c r="Q2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="R2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="27" t="s">
+      <c r="S2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="T2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="U2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="V2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="W2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="X2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="Y2" s="27" t="s">
+      <c r="Y2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="Z2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AA2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="AB2" s="27" t="s">
+      <c r="AB2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="27" t="s">
+      <c r="AC2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="AD2" s="27" t="s">
+      <c r="AD2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="AE2" s="27" t="s">
+      <c r="AE2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="AF2" s="27" t="s">
+      <c r="AF2" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="AG2" s="27" t="s">
+      <c r="AG2" s="23" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31">
+      <c r="C3" s="28">
+        <v>9.6</v>
+      </c>
+      <c r="D3" s="28">
+        <v>-13.4</v>
+      </c>
+      <c r="E3" s="32">
+        <v>3.6947535771065176</v>
+      </c>
+      <c r="F3" s="27">
         <v>22.344666666666665</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="27">
         <v>-1.8966666666666665</v>
       </c>
-      <c r="H3" s="31">
+      <c r="H3" s="27">
         <v>-24.788666666666668</v>
       </c>
-      <c r="I3" s="31">
+      <c r="I3" s="27">
         <v>1.153</v>
       </c>
-      <c r="J3" s="31">
+      <c r="J3" s="27">
         <v>20.632999999999999</v>
       </c>
-      <c r="K3" s="31">
+      <c r="K3" s="27">
         <v>21.044666666666668</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="27">
         <v>21.550333333333338</v>
       </c>
-      <c r="M3" s="31">
+      <c r="M3" s="27">
         <v>16.207000000000001</v>
       </c>
-      <c r="N3" s="31">
+      <c r="N3" s="27">
         <v>16.497</v>
       </c>
-      <c r="O3" s="31">
+      <c r="O3" s="27">
         <v>21.565333333333331</v>
       </c>
-      <c r="P3" s="31">
+      <c r="P3" s="27">
         <v>1.672666666666667</v>
       </c>
-      <c r="Q3" s="31">
+      <c r="Q3" s="27">
         <v>8.3843333333333323</v>
       </c>
-      <c r="R3" s="31">
+      <c r="R3" s="27">
         <v>0.66733333333333322</v>
       </c>
-      <c r="S3" s="31">
+      <c r="S3" s="27">
         <v>0.29987552973451115</v>
       </c>
-      <c r="T3" s="31">
+      <c r="T3" s="27">
         <v>0.50929591921920558</v>
       </c>
-      <c r="U3" s="31">
+      <c r="U3" s="27">
         <v>0.56572284144559382</v>
       </c>
-      <c r="V3" s="31">
+      <c r="V3" s="27">
         <v>0.46480963845428142</v>
       </c>
-      <c r="W3" s="31">
+      <c r="W3" s="27">
         <v>0.36346801785028354</v>
       </c>
-      <c r="X3" s="31">
+      <c r="X3" s="27">
         <v>0.16119966914768771</v>
       </c>
-      <c r="Y3" s="31">
+      <c r="Y3" s="27">
         <v>0.33771338933054657</v>
       </c>
-      <c r="Z3" s="31">
+      <c r="Z3" s="27">
         <v>0.70514962951130444</v>
       </c>
-      <c r="AA3" s="31">
+      <c r="AA3" s="27">
         <v>0.20217071993718466</v>
       </c>
-      <c r="AB3" s="31">
+      <c r="AB3" s="27">
         <v>0.21800305808241088</v>
       </c>
-      <c r="AC3" s="31">
+      <c r="AC3" s="27">
         <v>6.6500626563457413E-2</v>
       </c>
-      <c r="AD3" s="31">
+      <c r="AD3" s="27">
         <v>0.69905245392128057</v>
       </c>
-      <c r="AE3" s="31">
+      <c r="AE3" s="27">
         <v>5.3910419524739885E-2</v>
       </c>
-      <c r="AF3" s="31">
+      <c r="AF3" s="27">
         <v>0.23160526764296729</v>
       </c>
-      <c r="AG3" s="31">
+      <c r="AG3" s="27">
         <v>0.17099999999999937</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="31">
+      <c r="C4" s="28">
+        <v>10.3</v>
+      </c>
+      <c r="D4" s="28">
+        <v>-14.9</v>
+      </c>
+      <c r="E4" s="32">
+        <v>3.6466763005780352</v>
+      </c>
+      <c r="F4" s="27">
         <v>22.056333333333331</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="27">
         <v>-1.9813333333333334</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="27">
         <v>-28.028000000000002</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="27">
         <v>0.72133333333333327</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="27">
         <v>19.575333333333333</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="27">
         <v>21.599333333333334</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="27">
         <v>23.409000000000002</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="27">
         <v>16.514333333333337</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="27">
         <v>16.438666666666666</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="27">
         <v>20.62</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="27">
         <v>1.4556666666666667</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="27">
         <v>7.7866666666666662</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="27">
         <v>0.21366666666666667</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="27">
         <v>0.32038154337211899</v>
       </c>
-      <c r="T4" s="31">
+      <c r="T4" s="27">
         <v>0.24325363991795396</v>
       </c>
-      <c r="U4" s="31">
+      <c r="U4" s="27">
         <v>0.23305793271147035</v>
       </c>
-      <c r="V4" s="31">
+      <c r="V4" s="27">
         <v>0.43440342233151624</v>
       </c>
-      <c r="W4" s="31">
+      <c r="W4" s="27">
         <v>0.25197685078880305</v>
       </c>
-      <c r="X4" s="31">
+      <c r="X4" s="27">
         <v>9.9500418759588621E-2</v>
       </c>
-      <c r="Y4" s="31">
+      <c r="Y4" s="27">
         <v>0.18815153467346185</v>
       </c>
-      <c r="Z4" s="31">
+      <c r="Z4" s="27">
         <v>0.19805386472676173</v>
       </c>
-      <c r="AA4" s="31">
+      <c r="AA4" s="27">
         <v>0.38060521979246403</v>
       </c>
-      <c r="AB4" s="31">
+      <c r="AB4" s="27">
         <v>0.3390973311601379</v>
       </c>
-      <c r="AC4" s="31">
+      <c r="AC4" s="27">
         <v>0.1510110371242207</v>
       </c>
-      <c r="AD4" s="31">
+      <c r="AD4" s="27">
         <v>0.42163293672735286</v>
       </c>
-      <c r="AE4" s="31">
+      <c r="AE4" s="27">
         <v>0.13477512134416106</v>
       </c>
-      <c r="AF4" s="31">
+      <c r="AF4" s="27">
         <v>0.15452184311601513</v>
       </c>
-      <c r="AG4" s="31">
+      <c r="AG4" s="27">
         <v>0.40399999999999991</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="31">
+      <c r="C5" s="28">
+        <v>10.7</v>
+      </c>
+      <c r="D5" s="28">
+        <v>-13.9</v>
+      </c>
+      <c r="E5" s="32">
+        <v>3.6885699899295066</v>
+      </c>
+      <c r="F5" s="27">
         <v>23.094666666666669</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="27">
         <v>-1.5609999999999999</v>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="27">
         <v>-26.466333333333335</v>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="27">
         <v>1.4933333333333334</v>
       </c>
-      <c r="J5" s="31">
+      <c r="J5" s="27">
         <v>22.15433333333333</v>
       </c>
-      <c r="K5" s="31">
+      <c r="K5" s="27">
         <v>22.611000000000001</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="27">
         <v>23.575333333333333</v>
       </c>
-      <c r="M5" s="31">
+      <c r="M5" s="27">
         <v>19.396000000000001</v>
       </c>
-      <c r="N5" s="31">
+      <c r="N5" s="27">
         <v>17.696666666666665</v>
       </c>
-      <c r="O5" s="31">
+      <c r="O5" s="27">
         <v>23.173999999999996</v>
       </c>
-      <c r="P5" s="31">
+      <c r="P5" s="27">
         <v>2.5026666666666664</v>
       </c>
-      <c r="Q5" s="31">
+      <c r="Q5" s="27">
         <v>9.6786666666666665</v>
       </c>
-      <c r="R5" s="31">
+      <c r="R5" s="27">
         <v>1.7536666666666667</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="27">
         <v>4.4467216388406075E-2</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="27">
         <v>0.48373959937139743</v>
       </c>
-      <c r="U5" s="31">
+      <c r="U5" s="27">
         <v>0.43111522048434647</v>
       </c>
-      <c r="V5" s="31">
+      <c r="V5" s="27">
         <v>0.27770908039409264</v>
       </c>
-      <c r="W5" s="31">
+      <c r="W5" s="27">
         <v>0.11172436320397217</v>
       </c>
-      <c r="X5" s="31">
+      <c r="X5" s="27">
         <v>0.23088308729748477</v>
       </c>
-      <c r="Y5" s="31">
+      <c r="Y5" s="27">
         <v>0.37681604707524136</v>
       </c>
-      <c r="Z5" s="31">
+      <c r="Z5" s="27">
         <v>0.1681427964559154</v>
       </c>
-      <c r="AA5" s="31">
+      <c r="AA5" s="27">
         <v>0.12058330453812106</v>
       </c>
-      <c r="AB5" s="31">
+      <c r="AB5" s="27">
         <v>0.24920473510791588</v>
       </c>
-      <c r="AC5" s="31">
+      <c r="AC5" s="27">
         <v>0.25050415831545741</v>
       </c>
-      <c r="AD5" s="31">
+      <c r="AD5" s="27">
         <v>0.69051381835073145</v>
       </c>
-      <c r="AE5" s="31">
+      <c r="AE5" s="27">
         <v>0.40664029969167276</v>
       </c>
-      <c r="AF5" s="31">
+      <c r="AF5" s="27">
         <v>0.32466598220326576</v>
       </c>
-      <c r="AG5" s="31">
+      <c r="AG5" s="27">
         <v>0.39500000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31">
+      <c r="C6" s="28">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D6" s="28">
+        <v>-15.5</v>
+      </c>
+      <c r="E6" s="32">
+        <v>3.7020582329317269</v>
+      </c>
+      <c r="F6" s="27">
         <v>24.370161688659511</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="27">
         <v>-2.8300983259197934</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="27">
         <v>-33.464786473630063</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="27">
         <v>-0.29093048568994939</v>
       </c>
-      <c r="J6" s="31">
+      <c r="J6" s="27">
         <v>22.458525984118268</v>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="27">
         <v>23.456840369279764</v>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="27">
         <v>26.166702616621293</v>
       </c>
-      <c r="M6" s="31">
+      <c r="M6" s="27">
         <v>18.65260732596623</v>
       </c>
-      <c r="N6" s="31">
+      <c r="N6" s="27">
         <v>19.080405757067712</v>
       </c>
-      <c r="O6" s="31">
+      <c r="O6" s="27">
         <v>23.859849156194908</v>
       </c>
-      <c r="P6" s="31">
+      <c r="P6" s="27">
         <v>1.7981282436706987</v>
       </c>
-      <c r="Q6" s="31">
+      <c r="Q6" s="27">
         <v>8.2338740122197862</v>
       </c>
-      <c r="R6" s="31">
+      <c r="R6" s="27">
         <v>-0.51757866110795503</v>
       </c>
-      <c r="S6" s="31">
+      <c r="S6" s="27">
         <v>0.20410044796145274</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="27">
         <v>0.40317757383900682</v>
       </c>
-      <c r="U6" s="31">
+      <c r="U6" s="27">
         <v>0.45493666525831078</v>
       </c>
-      <c r="V6" s="31">
+      <c r="V6" s="27">
         <v>0.50378149085333268</v>
       </c>
-      <c r="W6" s="31">
+      <c r="W6" s="27">
         <v>0.30502982427272329</v>
       </c>
-      <c r="X6" s="31">
+      <c r="X6" s="27">
         <v>0.27898415524110748</v>
       </c>
-      <c r="Y6" s="31">
+      <c r="Y6" s="27">
         <v>0.90433176994555142</v>
       </c>
-      <c r="Z6" s="31">
+      <c r="Z6" s="27">
         <v>0.20622041928749885</v>
       </c>
-      <c r="AA6" s="31">
+      <c r="AA6" s="27">
         <v>0.53080952423900141</v>
       </c>
-      <c r="AB6" s="31">
+      <c r="AB6" s="27">
         <v>0.39875803284095812</v>
       </c>
-      <c r="AC6" s="31">
+      <c r="AC6" s="27">
         <v>0.22717351651028059</v>
       </c>
-      <c r="AD6" s="31">
+      <c r="AD6" s="27">
         <v>1.0537995929938127</v>
       </c>
-      <c r="AE6" s="31">
+      <c r="AE6" s="27">
         <v>0.39088148321904764</v>
       </c>
-      <c r="AF6" s="31">
+      <c r="AF6" s="27">
         <v>0.34815885962285253</v>
       </c>
-      <c r="AG6" s="31">
+      <c r="AG6" s="27">
         <v>0.23315688918117772</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="31">
+      <c r="C7" s="28">
+        <v>10</v>
+      </c>
+      <c r="D7" s="28">
+        <v>-15.5</v>
+      </c>
+      <c r="E7" s="32">
+        <v>3.6986584107327145</v>
+      </c>
+      <c r="F7" s="27">
         <v>21.184999999999999</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="27">
         <v>-2.9226666666666667</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="27">
         <v>-27.574666666666669</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="27">
         <v>1.2083333333333335</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="27">
         <v>18.446333333333332</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="27">
         <v>19.623999999999999</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="27">
         <v>20.624333333333333</v>
       </c>
-      <c r="M7" s="31">
+      <c r="M7" s="27">
         <v>16.189333333333334</v>
       </c>
-      <c r="N7" s="31">
+      <c r="N7" s="27">
         <v>15.823666666666668</v>
       </c>
-      <c r="O7" s="31">
+      <c r="O7" s="27">
         <v>20.268000000000001</v>
       </c>
-      <c r="P7" s="31">
+      <c r="P7" s="27">
         <v>1.9043333333333334</v>
       </c>
-      <c r="Q7" s="31">
+      <c r="Q7" s="27">
         <v>8.9906666666666677</v>
       </c>
-      <c r="R7" s="31">
+      <c r="R7" s="27">
         <v>1.9139999999999999</v>
       </c>
-      <c r="S7" s="31">
+      <c r="S7" s="27">
         <v>0.13173078607523783</v>
       </c>
-      <c r="T7" s="31">
+      <c r="T7" s="27">
         <v>0.29620994806611556</v>
       </c>
-      <c r="U7" s="31">
+      <c r="U7" s="27">
         <v>0.38317924439270618</v>
       </c>
-      <c r="V7" s="31">
+      <c r="V7" s="27">
         <v>0.56880605950827645</v>
       </c>
-      <c r="W7" s="31">
+      <c r="W7" s="27">
         <v>0.23078633697298295</v>
       </c>
-      <c r="X7" s="31">
+      <c r="X7" s="27">
         <v>0.48324320998849896</v>
       </c>
-      <c r="Y7" s="31">
+      <c r="Y7" s="27">
         <v>0.79371930386848155</v>
       </c>
-      <c r="Z7" s="31">
+      <c r="Z7" s="27">
         <v>0.5613379849372051</v>
       </c>
-      <c r="AA7" s="31">
+      <c r="AA7" s="27">
         <v>0.23450017768277037</v>
       </c>
-      <c r="AB7" s="31">
+      <c r="AB7" s="27">
         <v>0.33324315446828751</v>
       </c>
-      <c r="AC7" s="31">
+      <c r="AC7" s="27">
         <v>0.2318325545158246</v>
       </c>
-      <c r="AD7" s="31">
+      <c r="AD7" s="27">
         <v>6.7950962710865523E-2</v>
       </c>
-      <c r="AE7" s="31">
+      <c r="AE7" s="27">
         <v>0.1110720486891261</v>
       </c>
-      <c r="AF7" s="31">
+      <c r="AF7" s="27">
         <v>0.44472163578264601</v>
       </c>
-      <c r="AG7" s="31">
+      <c r="AG7" s="27">
         <v>1.7333333333333201E-2</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="31">
+      <c r="C8" s="28">
+        <v>10.9</v>
+      </c>
+      <c r="D8" s="28">
+        <v>-15.2</v>
+      </c>
+      <c r="E8" s="32">
+        <v>3.7042042042042045</v>
+      </c>
+      <c r="F8" s="27">
         <v>22.570666666666668</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="27">
         <v>-1.8679999999999997</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="27">
         <v>-30.133666666666667</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="27">
         <v>2.7873333333333332</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="27">
         <v>22.03</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="27">
         <v>21.932333333333332</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="27">
         <v>22.785666666666668</v>
       </c>
-      <c r="M8" s="31">
+      <c r="M8" s="27">
         <v>18.307333333333336</v>
       </c>
-      <c r="N8" s="31">
+      <c r="N8" s="27">
         <v>18.295666666666666</v>
       </c>
-      <c r="O8" s="31">
+      <c r="O8" s="27">
         <v>22.466666666666669</v>
       </c>
-      <c r="P8" s="31">
+      <c r="P8" s="27">
         <v>4.1000000000000009E-2</v>
       </c>
-      <c r="Q8" s="31">
+      <c r="Q8" s="27">
         <v>8.4553333333333338</v>
       </c>
-      <c r="R8" s="31">
+      <c r="R8" s="27">
         <v>1.3263333333333334</v>
       </c>
-      <c r="S8" s="31">
+      <c r="S8" s="27">
         <v>9.4001773032923827E-2</v>
       </c>
-      <c r="T8" s="31">
+      <c r="T8" s="27">
         <v>0.16928083175599262</v>
       </c>
-      <c r="U8" s="31">
+      <c r="U8" s="27">
         <v>0.66628922648759781</v>
       </c>
-      <c r="V8" s="31">
+      <c r="V8" s="27">
         <v>0.38417747634827837</v>
       </c>
-      <c r="W8" s="31">
+      <c r="W8" s="27">
         <v>0.92016302903347258</v>
       </c>
-      <c r="X8" s="31">
+      <c r="X8" s="27">
         <v>0.19055270487034245</v>
       </c>
-      <c r="Y8" s="31">
+      <c r="Y8" s="27">
         <v>0.40914585826238314</v>
       </c>
-      <c r="Z8" s="31">
+      <c r="Z8" s="27">
         <v>0.50709499438783534</v>
       </c>
-      <c r="AA8" s="31">
+      <c r="AA8" s="27">
         <v>0.23221613495500512</v>
       </c>
-      <c r="AB8" s="31">
+      <c r="AB8" s="27">
         <v>0.11664190213355288</v>
       </c>
-      <c r="AC8" s="31">
+      <c r="AC8" s="27">
         <v>0.19354844354837886</v>
       </c>
-      <c r="AD8" s="31">
+      <c r="AD8" s="27">
         <v>1.0579042174664737</v>
       </c>
-      <c r="AE8" s="31">
+      <c r="AE8" s="27">
         <v>0.38055792375580982</v>
       </c>
-      <c r="AF8" s="31">
+      <c r="AF8" s="27">
         <v>0.39119176882963097</v>
       </c>
-      <c r="AG8" s="31">
+      <c r="AG8" s="27">
         <v>-0.15800000000000125</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="31">
+      <c r="C9" s="28">
+        <v>10.6</v>
+      </c>
+      <c r="D9" s="28">
+        <v>-15</v>
+      </c>
+      <c r="E9" s="32">
+        <v>3.7150751547303269</v>
+      </c>
+      <c r="F9" s="27">
         <v>22.524666666666672</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="27">
         <v>-2.0396666666666667</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="27">
         <v>-29.213999999999999</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="27">
         <v>1.9713333333333332</v>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="27">
         <v>22.126333333333331</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="27">
         <v>22.337666666666667</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="27">
         <v>23.308666666666667</v>
       </c>
-      <c r="M9" s="31">
+      <c r="M9" s="27">
         <v>18.871333333333332</v>
       </c>
-      <c r="N9" s="31">
+      <c r="N9" s="27">
         <v>18.748999999999999</v>
       </c>
-      <c r="O9" s="31">
+      <c r="O9" s="27">
         <v>23.14833333333333</v>
       </c>
-      <c r="P9" s="31">
+      <c r="P9" s="27">
         <v>0.13399999999999998</v>
       </c>
-      <c r="Q9" s="31">
+      <c r="Q9" s="27">
         <v>8.9786666666666672</v>
       </c>
-      <c r="R9" s="31">
+      <c r="R9" s="27">
         <v>1.1693333333333333</v>
       </c>
-      <c r="S9" s="31">
+      <c r="S9" s="27">
         <v>0.59802536178080856</v>
       </c>
-      <c r="T9" s="31">
+      <c r="T9" s="27">
         <v>0.44108993791893897</v>
       </c>
-      <c r="U9" s="31">
+      <c r="U9" s="27">
         <v>0.48086276628598745</v>
       </c>
-      <c r="V9" s="31">
+      <c r="V9" s="27">
         <v>0.38634742568487884</v>
       </c>
-      <c r="W9" s="31">
+      <c r="W9" s="27">
         <v>0.70591949493796835</v>
       </c>
-      <c r="X9" s="31">
+      <c r="X9" s="27">
         <v>0.37980170264647845</v>
       </c>
-      <c r="Y9" s="31">
+      <c r="Y9" s="27">
         <v>0.39015680608349046</v>
       </c>
-      <c r="Z9" s="31">
+      <c r="Z9" s="27">
         <v>0.62120232882157245</v>
       </c>
-      <c r="AA9" s="31">
+      <c r="AA9" s="27">
         <v>0.11121600604229606</v>
       </c>
-      <c r="AB9" s="31">
+      <c r="AB9" s="27">
         <v>0.20750983912462664</v>
       </c>
-      <c r="AC9" s="31">
+      <c r="AC9" s="27">
         <v>0.52591919531426112</v>
       </c>
-      <c r="AD9" s="31">
+      <c r="AD9" s="27">
         <v>0.24116038922953001</v>
       </c>
-      <c r="AE9" s="31">
+      <c r="AE9" s="27">
         <v>0.81837420128773231</v>
       </c>
-      <c r="AF9" s="31">
+      <c r="AF9" s="27">
         <v>0.72777262932857378</v>
       </c>
-      <c r="AG9" s="31">
+      <c r="AG9" s="27">
         <v>-9.0000000000003411E-2</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="31">
+      <c r="C10" s="28">
+        <v>10.6</v>
+      </c>
+      <c r="D10" s="28">
+        <v>-16.399999999999999</v>
+      </c>
+      <c r="E10" s="32">
+        <v>3.7391838741396266</v>
+      </c>
+      <c r="F10" s="27">
         <v>23.138000000000002</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="27">
         <v>-1.4803333333333333</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="27">
         <v>-32.471000000000004</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="27">
         <v>2.1023333333333336</v>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="27">
         <v>22.518000000000001</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="27">
         <v>22.00033333333333</v>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="27">
         <v>22.519333333333336</v>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="27">
         <v>19.455666666666669</v>
       </c>
-      <c r="N10" s="31">
+      <c r="N10" s="27">
         <v>18.464333333333332</v>
       </c>
-      <c r="O10" s="31">
+      <c r="O10" s="27">
         <v>22.998999999999999</v>
       </c>
-      <c r="P10" s="31">
+      <c r="P10" s="27">
         <v>-0.31333333333333335</v>
       </c>
-      <c r="Q10" s="31">
+      <c r="Q10" s="27">
         <v>9.7313333333333336</v>
       </c>
-      <c r="R10" s="31">
+      <c r="R10" s="27">
         <v>0.85466666666666669</v>
       </c>
-      <c r="S10" s="31">
+      <c r="S10" s="27">
         <v>0.30998870947180673</v>
       </c>
-      <c r="T10" s="31">
+      <c r="T10" s="27">
         <v>0.44075654655754587</v>
       </c>
-      <c r="U10" s="31">
+      <c r="U10" s="27">
         <v>0.45008110380168964</v>
       </c>
-      <c r="V10" s="31">
+      <c r="V10" s="27">
         <v>0.7555013787765934</v>
       </c>
-      <c r="W10" s="31">
+      <c r="W10" s="27">
         <v>0.35050106989830293</v>
       </c>
-      <c r="X10" s="31">
+      <c r="X10" s="27">
         <v>0.37243030667952859</v>
       </c>
-      <c r="Y10" s="31">
+      <c r="Y10" s="27">
         <v>0.80355232146591571</v>
       </c>
-      <c r="Z10" s="31">
+      <c r="Z10" s="27">
         <v>0.37149203670247227</v>
       </c>
-      <c r="AA10" s="31">
+      <c r="AA10" s="27">
         <v>0.10027129865187399</v>
       </c>
-      <c r="AB10" s="31">
+      <c r="AB10" s="27">
         <v>0.26597556278746137</v>
       </c>
-      <c r="AC10" s="31">
+      <c r="AC10" s="27">
         <v>0.80562605055530168</v>
       </c>
-      <c r="AD10" s="31">
+      <c r="AD10" s="27">
         <v>0.88341685139765169</v>
       </c>
-      <c r="AE10" s="31">
+      <c r="AE10" s="27">
         <v>0.7660628781851615</v>
       </c>
-      <c r="AF10" s="31">
+      <c r="AF10" s="27">
         <v>0.17742698028575088</v>
       </c>
-      <c r="AG10" s="31">
+      <c r="AG10" s="27">
         <v>0.12066666666666492</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="31">
+      <c r="C11" s="28">
+        <v>10.1</v>
+      </c>
+      <c r="D11" s="28">
+        <v>-15.6</v>
+      </c>
+      <c r="E11" s="32">
+        <v>3.693862275449102</v>
+      </c>
+      <c r="F11" s="27">
         <v>22.853288619021068</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="27">
         <v>-2.9957766477270815</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="27">
         <v>-33.090346554500378</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="27">
         <v>0.78564448913741913</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="27">
         <v>21.360363910440796</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="27">
         <v>22.099810641100387</v>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="27">
         <v>26.590160545831594</v>
       </c>
-      <c r="M11" s="31">
+      <c r="M11" s="27">
         <v>18.59620820000552</v>
       </c>
-      <c r="N11" s="31">
+      <c r="N11" s="27">
         <v>17.865180217702587</v>
       </c>
-      <c r="O11" s="31">
+      <c r="O11" s="27">
         <v>22.691578494336976</v>
       </c>
-      <c r="P11" s="31">
+      <c r="P11" s="27">
         <v>0.7225038764625018</v>
       </c>
-      <c r="Q11" s="31">
+      <c r="Q11" s="27">
         <v>9.6298904189857186</v>
       </c>
-      <c r="R11" s="31">
+      <c r="R11" s="27">
         <v>-0.95738720187182969</v>
       </c>
-      <c r="S11" s="31">
+      <c r="S11" s="27">
         <v>0.10190540476111613</v>
       </c>
-      <c r="T11" s="31">
+      <c r="T11" s="27">
         <v>0.30894185056929496</v>
       </c>
-      <c r="U11" s="31">
+      <c r="U11" s="27">
         <v>0.21941888649431493</v>
       </c>
-      <c r="V11" s="31">
+      <c r="V11" s="27">
         <v>0.23111901688267394</v>
       </c>
-      <c r="W11" s="31">
+      <c r="W11" s="27">
         <v>0.52166634252981703</v>
       </c>
-      <c r="X11" s="31">
+      <c r="X11" s="27">
         <v>0.1159601095078767</v>
       </c>
-      <c r="Y11" s="31">
+      <c r="Y11" s="27">
         <v>0.84477190750547038</v>
       </c>
-      <c r="Z11" s="31">
+      <c r="Z11" s="27">
         <v>0.15657419717431523</v>
       </c>
-      <c r="AA11" s="31">
+      <c r="AA11" s="27">
         <v>9.3382272594881105E-2</v>
       </c>
-      <c r="AB11" s="31">
+      <c r="AB11" s="27">
         <v>4.3094720922355424E-2</v>
       </c>
-      <c r="AC11" s="31">
+      <c r="AC11" s="27">
         <v>0.1836402303200573</v>
       </c>
-      <c r="AD11" s="31">
+      <c r="AD11" s="27">
         <v>0.41823606586960443</v>
       </c>
-      <c r="AE11" s="31">
+      <c r="AE11" s="27">
         <v>5.9838786968227642E-2</v>
       </c>
-      <c r="AF11" s="31">
+      <c r="AF11" s="27">
         <v>0.11130160307215586</v>
       </c>
-      <c r="AG11" s="31">
+      <c r="AG11" s="27">
         <v>0.47606914134793499</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="31">
+      <c r="C12" s="28">
+        <v>10</v>
+      </c>
+      <c r="D12" s="28">
+        <v>-15.7</v>
+      </c>
+      <c r="E12" s="32">
+        <v>3.665277777777777</v>
+      </c>
+      <c r="F12" s="27">
         <v>22.758666666666667</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="27">
         <v>-4.0049999999999999</v>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="27">
         <v>-30.239666666666665</v>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="27">
         <v>-0.221</v>
       </c>
-      <c r="J12" s="31">
+      <c r="J12" s="27">
         <v>22.262666666666664</v>
       </c>
-      <c r="K12" s="31">
+      <c r="K12" s="27">
         <v>21.895</v>
       </c>
-      <c r="L12" s="31">
+      <c r="L12" s="27">
         <v>21.810999999999996</v>
       </c>
-      <c r="M12" s="31">
+      <c r="M12" s="27">
         <v>17.517666666666667</v>
       </c>
-      <c r="N12" s="31">
+      <c r="N12" s="27">
         <v>17.884666666666664</v>
       </c>
-      <c r="O12" s="31">
+      <c r="O12" s="27">
         <v>22.602000000000004</v>
       </c>
-      <c r="P12" s="31">
+      <c r="P12" s="27">
         <v>0.36333333333333329</v>
       </c>
-      <c r="Q12" s="31">
+      <c r="Q12" s="27">
         <v>8.3429999999999982</v>
       </c>
-      <c r="R12" s="31">
+      <c r="R12" s="27">
         <v>-0.22233333333333336</v>
       </c>
-      <c r="S12" s="31">
+      <c r="S12" s="27">
         <v>0.22795686726512676</v>
       </c>
-      <c r="T12" s="31">
+      <c r="T12" s="27">
         <v>0.46639468264549699</v>
       </c>
-      <c r="U12" s="31">
+      <c r="U12" s="27">
         <v>0.69604190486890749</v>
       </c>
-      <c r="V12" s="31">
+      <c r="V12" s="27">
         <v>0.24964975465639855</v>
       </c>
-      <c r="W12" s="31">
+      <c r="W12" s="27">
         <v>0.19769758049438807</v>
       </c>
-      <c r="X12" s="31">
+      <c r="X12" s="27">
         <v>0.19292226413778704</v>
       </c>
-      <c r="Y12" s="31">
+      <c r="Y12" s="27">
         <v>0.8313380780405617</v>
       </c>
-      <c r="Z12" s="31">
+      <c r="Z12" s="27">
         <v>0.281624454430627</v>
       </c>
-      <c r="AA12" s="31">
+      <c r="AA12" s="27">
         <v>0.28765488581513965</v>
       </c>
-      <c r="AB12" s="31">
+      <c r="AB12" s="27">
         <v>0.25664956652930382</v>
       </c>
-      <c r="AC12" s="31">
+      <c r="AC12" s="27">
         <v>0.16141974269999743</v>
       </c>
-      <c r="AD12" s="31">
+      <c r="AD12" s="27">
         <v>0.8237499620637373</v>
       </c>
-      <c r="AE12" s="31">
+      <c r="AE12" s="27">
         <v>0.69519589565340023</v>
       </c>
-      <c r="AF12" s="31">
+      <c r="AF12" s="27">
         <v>0.32653534775478854</v>
       </c>
-      <c r="AG12" s="31">
+      <c r="AG12" s="27">
         <v>0.1126666666666658</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="31">
+      <c r="C13" s="28">
+        <v>10.8</v>
+      </c>
+      <c r="D13" s="28">
+        <v>-15.7</v>
+      </c>
+      <c r="E13" s="32">
+        <v>3.985385572139303</v>
+      </c>
+      <c r="F13" s="27">
         <v>24.078333333333333</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="27">
         <v>-1.659</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="27">
         <v>-31.927000000000003</v>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="27">
         <v>1.9613333333333332</v>
       </c>
-      <c r="J13" s="31">
+      <c r="J13" s="27">
         <v>20.069333333333333</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="27">
         <v>22.120333333333331</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="27">
         <v>23.058999999999997</v>
       </c>
-      <c r="M13" s="31">
+      <c r="M13" s="27">
         <v>18.599</v>
       </c>
-      <c r="N13" s="31">
+      <c r="N13" s="27">
         <v>17.227333333333331</v>
       </c>
-      <c r="O13" s="31">
+      <c r="O13" s="27">
         <v>22.155000000000001</v>
       </c>
-      <c r="P13" s="31">
+      <c r="P13" s="27">
         <v>1.0953333333333333</v>
       </c>
-      <c r="Q13" s="31">
+      <c r="Q13" s="27">
         <v>9.022333333333334</v>
       </c>
-      <c r="R13" s="31">
+      <c r="R13" s="27">
         <v>1.2930000000000001</v>
       </c>
-      <c r="S13" s="31">
+      <c r="S13" s="27">
         <v>0.4998623143761225</v>
       </c>
-      <c r="T13" s="31">
+      <c r="T13" s="27">
         <v>0.77723355563176677</v>
       </c>
-      <c r="U13" s="31">
+      <c r="U13" s="27">
         <v>0.82990421133990455</v>
       </c>
-      <c r="V13" s="31">
+      <c r="V13" s="27">
         <v>7.3704364411710035E-2</v>
       </c>
-      <c r="W13" s="31">
+      <c r="W13" s="27">
         <v>0.90654306755572012</v>
       </c>
-      <c r="X13" s="31">
+      <c r="X13" s="27">
         <v>0.32994747056705398</v>
       </c>
-      <c r="Y13" s="31">
+      <c r="Y13" s="27">
         <v>0.74413909990012472</v>
       </c>
-      <c r="Z13" s="31">
+      <c r="Z13" s="27">
         <v>0.37476926234667157</v>
       </c>
-      <c r="AA13" s="31">
+      <c r="AA13" s="27">
         <v>0.18732947801494723</v>
       </c>
-      <c r="AB13" s="31">
+      <c r="AB13" s="27">
         <v>0.33530433936933535</v>
       </c>
-      <c r="AC13" s="31">
+      <c r="AC13" s="27">
         <v>9.5353727422336554E-2</v>
       </c>
-      <c r="AD13" s="31">
+      <c r="AD13" s="27">
         <v>0.38956685348387038</v>
       </c>
-      <c r="AE13" s="31">
+      <c r="AE13" s="27">
         <v>0.10762899237658986</v>
       </c>
-      <c r="AF13" s="31">
+      <c r="AF13" s="27">
         <v>6.9024150362995348E-2</v>
       </c>
-      <c r="AG13" s="31">
+      <c r="AG13" s="27">
         <v>0.3193333333333328</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31">
+      <c r="C14" s="28">
+        <v>10.4</v>
+      </c>
+      <c r="D14" s="28">
+        <v>-15.1</v>
+      </c>
+      <c r="E14" s="32">
+        <v>3.6878834355828221</v>
+      </c>
+      <c r="F14" s="27">
         <v>23.001999999999999</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="27">
         <v>-0.48799999999999999</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="27">
         <v>-25.407333333333337</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="27">
         <v>2.61</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="27">
         <v>21.582333333333334</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="27">
         <v>21.394000000000002</v>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="27">
         <v>22.478666666666665</v>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="27">
         <v>17.513000000000002</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="27">
         <v>18.040333333333333</v>
       </c>
-      <c r="O14" s="31">
+      <c r="O14" s="27">
         <v>22.828000000000003</v>
       </c>
-      <c r="P14" s="31">
+      <c r="P14" s="27">
         <v>-1.4850000000000001</v>
       </c>
-      <c r="Q14" s="31">
+      <c r="Q14" s="27">
         <v>7.6039999999999992</v>
       </c>
-      <c r="R14" s="31">
+      <c r="R14" s="27">
         <v>0.30833333333333329</v>
       </c>
-      <c r="S14" s="31">
+      <c r="S14" s="27">
         <v>0.21679714020259341</v>
       </c>
-      <c r="T14" s="31">
+      <c r="T14" s="27">
         <v>0.31033369137107897</v>
       </c>
-      <c r="U14" s="31">
+      <c r="U14" s="27">
         <v>0.23020932503533861</v>
       </c>
-      <c r="V14" s="31">
+      <c r="V14" s="27">
         <v>0.34877499910400667</v>
       </c>
-      <c r="W14" s="31">
+      <c r="W14" s="27">
         <v>0.22648914617108989</v>
       </c>
-      <c r="X14" s="31">
+      <c r="X14" s="27">
         <v>0.3315659813673012</v>
       </c>
-      <c r="Y14" s="31">
+      <c r="Y14" s="27">
         <v>0.70707590351633653</v>
       </c>
-      <c r="Z14" s="31">
+      <c r="Z14" s="27">
         <v>0.60395032908349067</v>
       </c>
-      <c r="AA14" s="31">
+      <c r="AA14" s="27">
         <v>0.13476770137274602</v>
       </c>
-      <c r="AB14" s="31">
+      <c r="AB14" s="27">
         <v>7.3573092907666213E-2</v>
       </c>
-      <c r="AC14" s="31">
+      <c r="AC14" s="27">
         <v>0.69262616179292535</v>
       </c>
-      <c r="AD14" s="31">
+      <c r="AD14" s="27">
         <v>0.39295801302430755</v>
       </c>
-      <c r="AE14" s="31">
+      <c r="AE14" s="27">
         <v>0.3960862700641532</v>
       </c>
-      <c r="AF14" s="31">
+      <c r="AF14" s="27">
         <v>0.34612473666767668</v>
       </c>
-      <c r="AG14" s="31">
+      <c r="AG14" s="27">
         <v>0.3176666666666641</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31">
+      <c r="C15" s="28">
+        <v>10.3</v>
+      </c>
+      <c r="D15" s="28">
+        <v>-15.9</v>
+      </c>
+      <c r="E15" s="32">
+        <v>3.6496913580246915</v>
+      </c>
+      <c r="F15" s="27">
         <v>24.414999999999999</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="27">
         <v>-0.65633333333333332</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="27">
         <v>-31.025666666666666</v>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="27">
         <v>1.6273333333333333</v>
       </c>
-      <c r="J15" s="31">
+      <c r="J15" s="27">
         <v>23.347999999999999</v>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="27">
         <v>22.659666666666666</v>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="27">
         <v>23.378333333333334</v>
       </c>
-      <c r="M15" s="31">
+      <c r="M15" s="27">
         <v>19.641000000000002</v>
       </c>
-      <c r="N15" s="31">
+      <c r="N15" s="27">
         <v>18.798333333333332</v>
       </c>
-      <c r="O15" s="31">
+      <c r="O15" s="27">
         <v>23.931333333333331</v>
       </c>
-      <c r="P15" s="31">
+      <c r="P15" s="27">
         <v>-0.70166666666666666</v>
       </c>
-      <c r="Q15" s="31">
+      <c r="Q15" s="27">
         <v>8.8346666666666653</v>
       </c>
-      <c r="R15" s="31">
+      <c r="R15" s="27">
         <v>1.3149999999999999</v>
       </c>
-      <c r="S15" s="31">
+      <c r="S15" s="27">
         <v>0.20018741219168013</v>
       </c>
-      <c r="T15" s="31">
+      <c r="T15" s="27">
         <v>0.43337897195564679</v>
       </c>
-      <c r="U15" s="31">
+      <c r="U15" s="27">
         <v>0.757233341403864</v>
       </c>
-      <c r="V15" s="31">
+      <c r="V15" s="27">
         <v>0.9850595582670798</v>
       </c>
-      <c r="W15" s="31">
+      <c r="W15" s="27">
         <v>0.34536212878660566</v>
       </c>
-      <c r="X15" s="31">
+      <c r="X15" s="27">
         <v>0.32753981946246002</v>
       </c>
-      <c r="Y15" s="31">
+      <c r="Y15" s="27">
         <v>0.55139308422687006</v>
       </c>
-      <c r="Z15" s="31">
+      <c r="Z15" s="27">
         <v>0.26438797249489038</v>
       </c>
-      <c r="AA15" s="31">
+      <c r="AA15" s="27">
         <v>0.20237671144028296</v>
       </c>
-      <c r="AB15" s="31">
+      <c r="AB15" s="27">
         <v>0.33283679684407369</v>
       </c>
-      <c r="AC15" s="31">
+      <c r="AC15" s="27">
         <v>0.86836301932621085</v>
       </c>
-      <c r="AD15" s="31">
+      <c r="AD15" s="27">
         <v>0.22555782702742738</v>
       </c>
-      <c r="AE15" s="31">
+      <c r="AE15" s="27">
         <v>0.23210342522246444</v>
       </c>
-      <c r="AF15" s="31">
+      <c r="AF15" s="27">
         <v>0.23979227121268326</v>
       </c>
-      <c r="AG15" s="31">
+      <c r="AG15" s="27">
         <v>0.3576666666666668</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31">
+      <c r="C16" s="28">
+        <v>10.9</v>
+      </c>
+      <c r="D16" s="28">
+        <v>-15.2</v>
+      </c>
+      <c r="E16" s="32">
+        <v>3.6976584022038574</v>
+      </c>
+      <c r="F16" s="27">
         <v>23.404666666666667</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="27">
         <v>-1.4076666666666668</v>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="27">
         <v>-29.466333333333335</v>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="27">
         <v>2.0383333333333336</v>
       </c>
-      <c r="J16" s="31">
+      <c r="J16" s="27">
         <v>22.677333333333333</v>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="27">
         <v>21.745999999999999</v>
       </c>
-      <c r="L16" s="31">
+      <c r="L16" s="27">
         <v>23.472999999999999</v>
       </c>
-      <c r="M16" s="31">
+      <c r="M16" s="27">
         <v>18.84</v>
       </c>
-      <c r="N16" s="31">
+      <c r="N16" s="27">
         <v>18.056000000000001</v>
       </c>
-      <c r="O16" s="31">
+      <c r="O16" s="27">
         <v>23.153666666666666</v>
       </c>
-      <c r="P16" s="31">
+      <c r="P16" s="27">
         <v>6.4333333333333326E-2</v>
       </c>
-      <c r="Q16" s="31">
+      <c r="Q16" s="27">
         <v>8.766</v>
       </c>
-      <c r="R16" s="31">
+      <c r="R16" s="27">
         <v>2.72</v>
       </c>
-      <c r="S16" s="31">
+      <c r="S16" s="27">
         <v>0.52104926190670919</v>
       </c>
-      <c r="T16" s="31">
+      <c r="T16" s="27">
         <v>0.4611467589968869</v>
       </c>
-      <c r="U16" s="31">
+      <c r="U16" s="27">
         <v>0.65815600987389444</v>
       </c>
-      <c r="V16" s="31">
+      <c r="V16" s="27">
         <v>0.22850455867079042</v>
       </c>
-      <c r="W16" s="31">
+      <c r="W16" s="27">
         <v>0.50987972437967677</v>
       </c>
-      <c r="X16" s="31">
+      <c r="X16" s="27">
         <v>0.33101812639182593</v>
       </c>
-      <c r="Y16" s="31">
+      <c r="Y16" s="27">
         <v>0.57859052878520445</v>
       </c>
-      <c r="Z16" s="31">
+      <c r="Z16" s="27">
         <v>0.17150218657524605</v>
       </c>
-      <c r="AA16" s="31">
+      <c r="AA16" s="27">
         <v>0.11705127081753622</v>
       </c>
-      <c r="AB16" s="31">
+      <c r="AB16" s="27">
         <v>5.7116839314980697E-2</v>
       </c>
-      <c r="AC16" s="31">
+      <c r="AC16" s="27">
         <v>0.19526989868726138</v>
       </c>
-      <c r="AD16" s="31">
+      <c r="AD16" s="27">
         <v>0.4283596619664215</v>
       </c>
-      <c r="AE16" s="31">
+      <c r="AE16" s="27">
         <v>7.0405965656334751E-2</v>
       </c>
-      <c r="AF16" s="31">
+      <c r="AF16" s="27">
         <v>3.8223029707234235E-2</v>
       </c>
-      <c r="AG16" s="31">
+      <c r="AG16" s="27">
         <v>-5.000000000002558E-3</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31">
+      <c r="C17" s="28">
+        <v>11.4</v>
+      </c>
+      <c r="D17" s="28">
+        <v>-13.6</v>
+      </c>
+      <c r="E17" s="32">
+        <v>3.8619729514717576</v>
+      </c>
+      <c r="F17" s="27">
         <v>21.240333333333336</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="27">
         <v>-0.94566666666666654</v>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="27">
         <v>-26.620999999999999</v>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="27">
         <v>1.8773333333333333</v>
       </c>
-      <c r="J17" s="31">
+      <c r="J17" s="27">
         <v>20.870666666666668</v>
       </c>
-      <c r="K17" s="31">
+      <c r="K17" s="27">
         <v>19.539333333333335</v>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="27">
         <v>21.244</v>
       </c>
-      <c r="M17" s="31">
+      <c r="M17" s="27">
         <v>16.09266666666667</v>
       </c>
-      <c r="N17" s="31">
+      <c r="N17" s="27">
         <v>16.873333333333331</v>
       </c>
-      <c r="O17" s="31">
+      <c r="O17" s="27">
         <v>22.873999999999999</v>
       </c>
-      <c r="P17" s="31">
+      <c r="P17" s="27">
         <v>-0.504</v>
       </c>
-      <c r="Q17" s="31">
+      <c r="Q17" s="27">
         <v>8.240333333333334</v>
       </c>
-      <c r="R17" s="31">
+      <c r="R17" s="27">
         <v>1.5956666666666666</v>
       </c>
-      <c r="S17" s="31">
+      <c r="S17" s="27">
         <v>0.1494835553946291</v>
       </c>
-      <c r="T17" s="31">
+      <c r="T17" s="27">
         <v>0.63200026371302531</v>
       </c>
-      <c r="U17" s="31">
+      <c r="U17" s="27">
         <v>0.26485656495526255</v>
       </c>
-      <c r="V17" s="31">
+      <c r="V17" s="27">
         <v>0.40177398289751692</v>
       </c>
-      <c r="W17" s="31">
+      <c r="W17" s="27">
         <v>0.24087410266210588</v>
       </c>
-      <c r="X17" s="31">
+      <c r="X17" s="27">
         <v>0.10539607835841645</v>
       </c>
-      <c r="Y17" s="31">
+      <c r="Y17" s="27">
         <v>0.30843637917716332</v>
       </c>
-      <c r="Z17" s="31">
+      <c r="Z17" s="27">
         <v>0.24404985829385753</v>
       </c>
-      <c r="AA17" s="31">
+      <c r="AA17" s="27">
         <v>0.11050037707326367</v>
       </c>
-      <c r="AB17" s="31">
+      <c r="AB17" s="27">
         <v>0.33288286228026032</v>
       </c>
-      <c r="AC17" s="31">
+      <c r="AC17" s="27">
         <v>0.29192293503594391</v>
       </c>
-      <c r="AD17" s="31">
+      <c r="AD17" s="27">
         <v>0.94985384840686271</v>
       </c>
-      <c r="AE17" s="31">
+      <c r="AE17" s="27">
         <v>0.30306654934738947</v>
       </c>
-      <c r="AF17" s="31">
+      <c r="AF17" s="27">
         <v>0.19738540979522495</v>
       </c>
-      <c r="AG17" s="31">
+      <c r="AG17" s="27">
         <v>0.74599999999999866</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="31">
+      <c r="C18" s="28">
+        <v>11.2</v>
+      </c>
+      <c r="D18" s="28">
+        <v>-14.1</v>
+      </c>
+      <c r="E18" s="32">
+        <v>3.7958287596048299</v>
+      </c>
+      <c r="F18" s="27">
         <v>21.692004423494357</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="27">
         <v>-2.4087451797628332</v>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="27">
         <v>-29.028004108284787</v>
       </c>
-      <c r="I18" s="31">
+      <c r="I18" s="27">
         <v>-6.3171256670799494</v>
       </c>
-      <c r="J18" s="31">
+      <c r="J18" s="27">
         <v>22.640325550124313</v>
       </c>
-      <c r="K18" s="31">
+      <c r="K18" s="27">
         <v>21.586325386580466</v>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="27">
         <v>24.154360861158011</v>
       </c>
-      <c r="M18" s="31">
+      <c r="M18" s="27">
         <v>16.286678634413448</v>
       </c>
-      <c r="N18" s="31">
+      <c r="N18" s="27">
         <v>18.164138224207136</v>
       </c>
-      <c r="O18" s="31">
+      <c r="O18" s="27">
         <v>24.624161728230664</v>
       </c>
-      <c r="P18" s="31">
+      <c r="P18" s="27">
         <v>3.7218800029683731E-2</v>
       </c>
-      <c r="Q18" s="31">
+      <c r="Q18" s="27">
         <v>9.9295439617087293</v>
       </c>
-      <c r="R18" s="31">
+      <c r="R18" s="27">
         <v>0.8170812638563012</v>
       </c>
-      <c r="S18" s="31">
+      <c r="S18" s="27">
         <v>0.1501409507571074</v>
       </c>
-      <c r="T18" s="31">
+      <c r="T18" s="27">
         <v>0.11662832013525584</v>
       </c>
-      <c r="U18" s="31">
+      <c r="U18" s="27">
         <v>0.56420320633593468</v>
       </c>
-      <c r="V18" s="31">
+      <c r="V18" s="27">
         <v>0.70883338975236565</v>
       </c>
-      <c r="W18" s="31">
+      <c r="W18" s="27">
         <v>0.58171865935276534</v>
       </c>
-      <c r="X18" s="31">
+      <c r="X18" s="27">
         <v>0.23088134665068358</v>
       </c>
-      <c r="Y18" s="31">
+      <c r="Y18" s="27">
         <v>0.91879932093286443</v>
       </c>
-      <c r="Z18" s="31">
+      <c r="Z18" s="27">
         <v>0.25112794938872479</v>
       </c>
-      <c r="AA18" s="31">
+      <c r="AA18" s="27">
         <v>6.2537924087599769E-2</v>
       </c>
-      <c r="AB18" s="31">
+      <c r="AB18" s="27">
         <v>0.25290904153272636</v>
       </c>
-      <c r="AC18" s="31">
+      <c r="AC18" s="27">
         <v>0.38183102769922939</v>
       </c>
-      <c r="AD18" s="31">
+      <c r="AD18" s="27">
         <v>0.67016685677863008</v>
       </c>
-      <c r="AE18" s="31">
+      <c r="AE18" s="27">
         <v>0.60987168517966694</v>
       </c>
-      <c r="AF18" s="31">
+      <c r="AF18" s="27">
         <v>0.24037377280125066</v>
       </c>
-      <c r="AG18" s="31">
+      <c r="AG18" s="27">
         <v>0.48988686170780937</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31">
+      <c r="C19" s="28">
+        <v>11.4</v>
+      </c>
+      <c r="D19" s="28">
+        <v>-14</v>
+      </c>
+      <c r="E19" s="32">
+        <v>3.9448924731182791</v>
+      </c>
+      <c r="F19" s="27">
         <v>21.362501221487875</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="27">
         <v>-2.3401847254770276</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="27">
         <v>-28.158651974841547</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="27">
         <v>1.2821306231031675</v>
       </c>
-      <c r="J19" s="31">
+      <c r="J19" s="27">
         <v>23.115876419615077</v>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="27">
         <v>21.070621160628786</v>
       </c>
-      <c r="L19" s="31">
+      <c r="L19" s="27">
         <v>24.193318845226496</v>
       </c>
-      <c r="M19" s="31">
+      <c r="M19" s="27">
         <v>15.738922106347516</v>
       </c>
-      <c r="N19" s="31">
+      <c r="N19" s="27">
         <v>17.546064684106657</v>
       </c>
-      <c r="O19" s="31">
+      <c r="O19" s="27">
         <v>23.589308671439152</v>
       </c>
-      <c r="P19" s="31">
+      <c r="P19" s="27">
         <v>-0.25652419532506587</v>
       </c>
-      <c r="Q19" s="31">
+      <c r="Q19" s="27">
         <v>8.2764287800291481</v>
       </c>
-      <c r="R19" s="31">
+      <c r="R19" s="27">
         <v>0.37890847305237568</v>
       </c>
-      <c r="S19" s="31">
+      <c r="S19" s="27">
         <v>0.52847983278997535</v>
       </c>
-      <c r="T19" s="31">
+      <c r="T19" s="27">
         <v>0.57410368108098164</v>
       </c>
-      <c r="U19" s="31">
+      <c r="U19" s="27">
         <v>0.22163276750959746</v>
       </c>
-      <c r="V19" s="31">
+      <c r="V19" s="27">
         <v>0.45640725198211968</v>
       </c>
-      <c r="W19" s="31">
+      <c r="W19" s="27">
         <v>2.1108236857982239</v>
       </c>
-      <c r="X19" s="31">
+      <c r="X19" s="27">
         <v>0.42481358490903937</v>
       </c>
-      <c r="Y19" s="31">
+      <c r="Y19" s="27">
         <v>0.97734472937585104</v>
       </c>
-      <c r="Z19" s="31">
+      <c r="Z19" s="27">
         <v>0.33009465308849673</v>
       </c>
-      <c r="AA19" s="31">
+      <c r="AA19" s="27">
         <v>0.15136164871365618</v>
       </c>
-      <c r="AB19" s="31">
+      <c r="AB19" s="27">
         <v>0.26471746520540584</v>
       </c>
-      <c r="AC19" s="31">
+      <c r="AC19" s="27">
         <v>0.58135892571292225</v>
       </c>
-      <c r="AD19" s="31">
+      <c r="AD19" s="27">
         <v>0.34984181037101775</v>
       </c>
-      <c r="AE19" s="31">
+      <c r="AE19" s="27">
         <v>7.8016709936861162E-2</v>
       </c>
-      <c r="AF19" s="31">
+      <c r="AF19" s="27">
         <v>0.38184664230210613</v>
       </c>
-      <c r="AG19" s="31">
+      <c r="AG19" s="27">
         <v>0.29404424814016394</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31">
+      <c r="C20" s="28">
+        <v>11.5</v>
+      </c>
+      <c r="D20" s="28">
+        <v>-14.1</v>
+      </c>
+      <c r="E20" s="32">
+        <v>3.8581997533908754</v>
+      </c>
+      <c r="F20" s="27">
         <v>20.830027455137945</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="27">
         <v>-3.4683946866270663</v>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="27">
         <v>-29.207203287669909</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="27">
         <v>0.12373579769654981</v>
       </c>
-      <c r="J20" s="31">
+      <c r="J20" s="27">
         <v>22.718087550544464</v>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="27">
         <v>21.397242425991397</v>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="27">
         <v>25.007044238056938</v>
       </c>
-      <c r="M20" s="31">
+      <c r="M20" s="27">
         <v>15.549418929904812</v>
       </c>
-      <c r="N20" s="31">
+      <c r="N20" s="27">
         <v>18.091664648384832</v>
       </c>
-      <c r="O20" s="31">
+      <c r="O20" s="27">
         <v>23.983146718892637</v>
       </c>
-      <c r="P20" s="31">
+      <c r="P20" s="27">
         <v>-1.0165845865909995</v>
       </c>
-      <c r="Q20" s="31">
+      <c r="Q20" s="27">
         <v>8.8720825198150663</v>
       </c>
-      <c r="R20" s="31">
+      <c r="R20" s="27">
         <v>-0.18637867934306027</v>
       </c>
-      <c r="S20" s="31">
+      <c r="S20" s="27">
         <v>0.20092651684272872</v>
       </c>
-      <c r="T20" s="31">
+      <c r="T20" s="27">
         <v>0.36478097385453206</v>
       </c>
-      <c r="U20" s="31">
+      <c r="U20" s="27">
         <v>0.16703473371982047</v>
       </c>
-      <c r="V20" s="31">
+      <c r="V20" s="27">
         <v>0.43354620550377498</v>
       </c>
-      <c r="W20" s="31">
+      <c r="W20" s="27">
         <v>0.54994548470803539</v>
       </c>
-      <c r="X20" s="31">
+      <c r="X20" s="27">
         <v>0.30002746173923767</v>
       </c>
-      <c r="Y20" s="31">
+      <c r="Y20" s="27">
         <v>0.92717854068457373</v>
       </c>
-      <c r="Z20" s="31">
+      <c r="Z20" s="27">
         <v>0.30569015251911019</v>
       </c>
-      <c r="AA20" s="31">
+      <c r="AA20" s="27">
         <v>0.25541008518393493</v>
       </c>
-      <c r="AB20" s="31">
+      <c r="AB20" s="27">
         <v>0.40944862394224291</v>
       </c>
-      <c r="AC20" s="31">
+      <c r="AC20" s="27">
         <v>0.46378181365443499</v>
       </c>
-      <c r="AD20" s="31">
+      <c r="AD20" s="27">
         <v>0.35382429259802012</v>
       </c>
-      <c r="AE20" s="31">
+      <c r="AE20" s="27">
         <v>0.10164878679397343</v>
       </c>
-      <c r="AF20" s="31">
+      <c r="AF20" s="27">
         <v>0.23591687618073295</v>
       </c>
-      <c r="AG20" s="31">
+      <c r="AG20" s="27">
         <v>0.29134102786436067</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31">
+      <c r="C21" s="28">
+        <v>11.3</v>
+      </c>
+      <c r="D21" s="28">
+        <v>-12.4</v>
+      </c>
+      <c r="E21" s="32">
+        <v>3.760416666666667</v>
+      </c>
+      <c r="F21" s="27">
         <v>21.803083798850537</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="27">
         <v>-1.5440100624507025</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="27">
         <v>-29.22202653775734</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="27">
         <v>0.8620965289087078</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="27">
         <v>20.348824526479039</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="27">
         <v>20.751169591835154</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="27">
         <v>23.792302732130121</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="27">
         <v>15.647065798018913</v>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="27">
         <v>17.67021744765383</v>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="27">
         <v>23.413849069105822</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="27">
         <v>-0.51910352763650536</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="27">
         <v>7.4516222937901206</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="27">
         <v>-0.27845824327979379</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="27">
         <v>0.18475078174463178</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="27">
         <v>0.21217690010845025</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="27">
         <v>1.1594614890236628</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="27">
         <v>0.50019879631816544</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="27">
         <v>0.59733594014834357</v>
       </c>
-      <c r="X21" s="31">
+      <c r="X21" s="27">
         <v>0.17647554856504599</v>
       </c>
-      <c r="Y21" s="31">
+      <c r="Y21" s="27">
         <v>0.20158927236338856</v>
       </c>
-      <c r="Z21" s="31">
+      <c r="Z21" s="27">
         <v>0.38591218231100433</v>
       </c>
-      <c r="AA21" s="31">
+      <c r="AA21" s="27">
         <v>0.14607740074836179</v>
       </c>
-      <c r="AB21" s="31">
+      <c r="AB21" s="27">
         <v>8.9310922806761853E-2</v>
       </c>
-      <c r="AC21" s="31">
+      <c r="AC21" s="27">
         <v>0.54370186073833959</v>
       </c>
-      <c r="AD21" s="31">
+      <c r="AD21" s="27">
         <v>0.96081468903316969</v>
       </c>
-      <c r="AE21" s="31">
+      <c r="AE21" s="27">
         <v>0.1845043479062996</v>
       </c>
-      <c r="AF21" s="31">
+      <c r="AF21" s="27">
         <v>0.1327510373292731</v>
       </c>
-      <c r="AG21" s="31">
+      <c r="AG21" s="27">
         <v>0.81708140079796721</v>
       </c>
     </row>
@@ -8802,5 +8949,6 @@
     <mergeCell ref="S1:AE1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>